--- a/Mon-Heros-Systeme-de-jeu.xlsx
+++ b/Mon-Heros-Systeme-de-jeu.xlsx
@@ -1029,7 +1029,7 @@
     <t xml:space="preserve">Seance normale + 1 PR + nutrition parfaite</t>
   </si>
   <si>
-    <t xml:space="preserve">Grosse seance, tout aligne (streak 10 sem.)</t>
+    <t xml:space="preserve">Grosse seance, tout aligne (streak entrainement 10 sem. + serie nutri 15 j)</t>
   </si>
   <si>
     <t xml:space="preserve">Grosse seance mais moral au plancher</t>
@@ -2483,7 +2483,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2652,6 +2652,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2664,11 +2668,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2680,7 +2684,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3418,11 +3422,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="76892166"/>
-        <c:axId val="8153202"/>
+        <c:axId val="87034853"/>
+        <c:axId val="70999295"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76892166"/>
+        <c:axId val="87034853"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3488,7 +3492,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8153202"/>
+        <c:crossAx val="70999295"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3496,7 +3500,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8153202"/>
+        <c:axId val="70999295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3572,7 +3576,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76892166"/>
+        <c:crossAx val="87034853"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4064,11 +4068,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24259631"/>
-        <c:axId val="50664258"/>
+        <c:axId val="86473489"/>
+        <c:axId val="94045200"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="24259631"/>
+        <c:axId val="86473489"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4134,7 +4138,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50664258"/>
+        <c:crossAx val="94045200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4142,7 +4146,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50664258"/>
+        <c:axId val="94045200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4218,7 +4222,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24259631"/>
+        <c:crossAx val="86473489"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4281,9 +4285,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>469080</xdr:colOff>
+      <xdr:colOff>468720</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4292,7 +4296,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11677680" y="570600"/>
-        <a:ext cx="7195680" cy="2868480"/>
+        <a:ext cx="7195320" cy="2868120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4316,9 +4320,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>360720</xdr:colOff>
+      <xdr:colOff>360360</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:rowOff>85320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4327,7 +4331,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11043360" y="570600"/>
-        <a:ext cx="6475680" cy="2867760"/>
+        <a:ext cx="6475320" cy="2867400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4972,7 +4976,7 @@
       <c r="A4" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="B4" s="58" t="n">
+      <c r="B4" s="59" t="n">
         <v>20</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -5015,22 +5019,22 @@
         <f aca="false">Parametres!$B$75</f>
         <v>70</v>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="101" t="n">
+      <c r="D8" s="102" t="n">
         <f aca="false">B8*(1+$B$4*Parametres!$B$80*C8)</f>
         <v>70</v>
       </c>
-      <c r="E8" s="88" t="n">
+      <c r="E8" s="89" t="n">
         <f aca="false">D8/SUM($D$8:$D$12)</f>
         <v>0.648628613787991</v>
       </c>
-      <c r="F8" s="93" t="n">
+      <c r="F8" s="94" t="n">
         <f aca="false">1/E8</f>
         <v>1.54171428571429</v>
       </c>
-      <c r="G8" s="71" t="n">
+      <c r="G8" s="72" t="n">
         <f aca="false">F8/Parametres!$B$74</f>
         <v>15.4171428571429</v>
       </c>
@@ -5043,22 +5047,22 @@
         <f aca="false">Parametres!$B$76</f>
         <v>22</v>
       </c>
-      <c r="C9" s="50" t="n">
+      <c r="C9" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="101" t="n">
+      <c r="D9" s="102" t="n">
         <f aca="false">B9*(1+$B$4*Parametres!$B$80*C9)</f>
         <v>26.4</v>
       </c>
-      <c r="E9" s="88" t="n">
+      <c r="E9" s="89" t="n">
         <f aca="false">D9/SUM($D$8:$D$12)</f>
         <v>0.244625648628614</v>
       </c>
-      <c r="F9" s="93" t="n">
+      <c r="F9" s="94" t="n">
         <f aca="false">1/E9</f>
         <v>4.08787878787879</v>
       </c>
-      <c r="G9" s="71" t="n">
+      <c r="G9" s="72" t="n">
         <f aca="false">F9/Parametres!$B$74</f>
         <v>40.8787878787879</v>
       </c>
@@ -5071,22 +5075,22 @@
         <f aca="false">Parametres!$B$77</f>
         <v>6.5</v>
       </c>
-      <c r="C10" s="50" t="n">
+      <c r="C10" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="101" t="n">
+      <c r="D10" s="102" t="n">
         <f aca="false">B10*(1+$B$4*Parametres!$B$80*C10)</f>
         <v>9.1</v>
       </c>
-      <c r="E10" s="88" t="n">
+      <c r="E10" s="89" t="n">
         <f aca="false">D10/SUM($D$8:$D$12)</f>
         <v>0.0843217197924388</v>
       </c>
-      <c r="F10" s="93" t="n">
+      <c r="F10" s="94" t="n">
         <f aca="false">1/E10</f>
         <v>11.8593406593407</v>
       </c>
-      <c r="G10" s="71" t="n">
+      <c r="G10" s="72" t="n">
         <f aca="false">F10/Parametres!$B$74</f>
         <v>118.593406593407</v>
       </c>
@@ -5099,22 +5103,22 @@
         <f aca="false">Parametres!$B$78</f>
         <v>1.4</v>
       </c>
-      <c r="C11" s="50" t="n">
+      <c r="C11" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="101" t="n">
+      <c r="D11" s="102" t="n">
         <f aca="false">B11*(1+$B$4*Parametres!$B$80*C11)</f>
         <v>2.24</v>
       </c>
-      <c r="E11" s="88" t="n">
+      <c r="E11" s="89" t="n">
         <f aca="false">D11/SUM($D$8:$D$12)</f>
         <v>0.0207561156412157</v>
       </c>
-      <c r="F11" s="93" t="n">
+      <c r="F11" s="94" t="n">
         <f aca="false">1/E11</f>
         <v>48.1785714285714</v>
       </c>
-      <c r="G11" s="71" t="n">
+      <c r="G11" s="72" t="n">
         <f aca="false">F11/Parametres!$B$74</f>
         <v>481.785714285714</v>
       </c>
@@ -5127,22 +5131,22 @@
         <f aca="false">Parametres!$B$79</f>
         <v>0.1</v>
       </c>
-      <c r="C12" s="50" t="n">
+      <c r="C12" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="101" t="n">
+      <c r="D12" s="102" t="n">
         <f aca="false">B12*(1+$B$4*Parametres!$B$80*C12)</f>
         <v>0.18</v>
       </c>
-      <c r="E12" s="88" t="n">
+      <c r="E12" s="89" t="n">
         <f aca="false">D12/SUM($D$8:$D$12)</f>
         <v>0.00166790214974055</v>
       </c>
-      <c r="F12" s="93" t="n">
+      <c r="F12" s="94" t="n">
         <f aca="false">1/E12</f>
         <v>599.555555555556</v>
       </c>
-      <c r="G12" s="71" t="n">
+      <c r="G12" s="72" t="n">
         <f aca="false">F12/Parametres!$B$74</f>
         <v>5995.55555555556</v>
       </c>
@@ -5151,11 +5155,11 @@
       <c r="A13" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="D13" s="79" t="n">
+      <c r="D13" s="80" t="n">
         <f aca="false">SUM(D8:D12)</f>
         <v>107.92</v>
       </c>
-      <c r="E13" s="102" t="n">
+      <c r="E13" s="103" t="n">
         <f aca="false">SUM(E8:E12)</f>
         <v>1</v>
       </c>
@@ -5183,7 +5187,7 @@
       <c r="A17" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="103" t="n">
+      <c r="B17" s="104" t="n">
         <f aca="false">1-(1-$E$11)^A17</f>
         <v>0.189209447751426</v>
       </c>
@@ -5200,7 +5204,7 @@
       <c r="A18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B18" s="103" t="n">
+      <c r="B18" s="104" t="n">
         <f aca="false">1-(1-$E$11)^A18</f>
         <v>0.342618680384453</v>
       </c>
@@ -5217,7 +5221,7 @@
       <c r="A19" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="B19" s="103" t="n">
+      <c r="B19" s="104" t="n">
         <f aca="false">1-(1-$E$11)^A19</f>
         <v>0.467001436831014</v>
       </c>
@@ -5234,7 +5238,7 @@
       <c r="A20" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="B20" s="103" t="n">
+      <c r="B20" s="104" t="n">
         <f aca="false">1-(1-$E$11)^A20</f>
         <v>0.567849800620522</v>
       </c>
@@ -5251,7 +5255,7 @@
       <c r="A21" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="B21" s="103" t="n">
+      <c r="B21" s="104" t="n">
         <f aca="false">1-(1-$E$11)^A21</f>
         <v>0.649616701190781</v>
       </c>
@@ -5268,7 +5272,7 @@
       <c r="A22" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="B22" s="103" t="n">
+      <c r="B22" s="104" t="n">
         <f aca="false">1-(1-$E$11)^A22</f>
         <v>0.715912531659797</v>
       </c>
@@ -5285,7 +5289,7 @@
       <c r="A23" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="B23" s="103" t="n">
+      <c r="B23" s="104" t="n">
         <f aca="false">1-(1-$E$11)^A23</f>
         <v>0.813246205176277</v>
       </c>
@@ -5327,7 +5331,7 @@
         <f aca="false">IF(A28&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A28-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.0207561156412157</v>
       </c>
-      <c r="C28" s="57" t="str">
+      <c r="C28" s="58" t="str">
         <f aca="false">IF(A28&gt;=Parametres!$B$83,"GARANTI",IF(A28&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Taux de base</v>
       </c>
@@ -5340,7 +5344,7 @@
         <f aca="false">IF(A29&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A29-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.0207561156412157</v>
       </c>
-      <c r="C29" s="57" t="str">
+      <c r="C29" s="58" t="str">
         <f aca="false">IF(A29&gt;=Parametres!$B$83,"GARANTI",IF(A29&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Taux de base</v>
       </c>
@@ -5353,7 +5357,7 @@
         <f aca="false">IF(A30&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A30-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.0207561156412157</v>
       </c>
-      <c r="C30" s="57" t="str">
+      <c r="C30" s="58" t="str">
         <f aca="false">IF(A30&gt;=Parametres!$B$83,"GARANTI",IF(A30&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Taux de base</v>
       </c>
@@ -5366,7 +5370,7 @@
         <f aca="false">IF(A31&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A31-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.0207561156412157</v>
       </c>
-      <c r="C31" s="57" t="str">
+      <c r="C31" s="58" t="str">
         <f aca="false">IF(A31&gt;=Parametres!$B$83,"GARANTI",IF(A31&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Pity doux actif</v>
       </c>
@@ -5379,7 +5383,7 @@
         <f aca="false">IF(A32&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A32-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.170756115641216</v>
       </c>
-      <c r="C32" s="57" t="str">
+      <c r="C32" s="58" t="str">
         <f aca="false">IF(A32&gt;=Parametres!$B$83,"GARANTI",IF(A32&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Pity doux actif</v>
       </c>
@@ -5392,7 +5396,7 @@
         <f aca="false">IF(A33&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A33-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.320756115641216</v>
       </c>
-      <c r="C33" s="57" t="str">
+      <c r="C33" s="58" t="str">
         <f aca="false">IF(A33&gt;=Parametres!$B$83,"GARANTI",IF(A33&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Pity doux actif</v>
       </c>
@@ -5405,7 +5409,7 @@
         <f aca="false">IF(A34&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A34-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.470756115641216</v>
       </c>
-      <c r="C34" s="57" t="str">
+      <c r="C34" s="58" t="str">
         <f aca="false">IF(A34&gt;=Parametres!$B$83,"GARANTI",IF(A34&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Pity doux actif</v>
       </c>
@@ -5418,7 +5422,7 @@
         <f aca="false">IF(A35&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A35-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>0.590756115641216</v>
       </c>
-      <c r="C35" s="57" t="str">
+      <c r="C35" s="58" t="str">
         <f aca="false">IF(A35&gt;=Parametres!$B$83,"GARANTI",IF(A35&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>Pity doux actif</v>
       </c>
@@ -5431,7 +5435,7 @@
         <f aca="false">IF(A36&gt;=Parametres!$B$83,1,MIN(1,$E$11+MAX(0,A36-Parametres!$B$81)*Parametres!$B$82))</f>
         <v>1</v>
       </c>
-      <c r="C36" s="57" t="str">
+      <c r="C36" s="58" t="str">
         <f aca="false">IF(A36&gt;=Parametres!$B$83,"GARANTI",IF(A36&gt;=Parametres!$B$81,"Pity doux actif","Taux de base"))</f>
         <v>GARANTI</v>
       </c>
@@ -5486,7 +5490,7 @@
       <c r="A5" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="59" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5494,7 +5498,7 @@
       <c r="A6" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="59" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5502,7 +5506,7 @@
       <c r="A7" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="B7" s="58" t="n">
+      <c r="B7" s="59" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5537,17 +5541,17 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="96" t="s">
         <v>629</v>
       </c>
       <c r="B12" s="36" t="s">
         <v>630</v>
       </c>
-      <c r="C12" s="104" t="n">
+      <c r="C12" s="105" t="n">
         <f aca="false">ROUND($B$6*Parametres!$B$63*55*(1+Parametres!$B$64*($B$7-1)),0)</f>
         <v>3300</v>
       </c>
-      <c r="D12" s="93" t="n">
+      <c r="D12" s="94" t="n">
         <f aca="false">C12*4.345</f>
         <v>14338.5</v>
       </c>
@@ -5556,17 +5560,17 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="95" t="s">
+      <c r="A13" s="96" t="s">
         <v>411</v>
       </c>
       <c r="B13" s="36" t="s">
         <v>630</v>
       </c>
-      <c r="C13" s="104" t="n">
+      <c r="C13" s="105" t="n">
         <f aca="false">ROUND($B$6*(Parametres!$B$65*Parametres!$B$51+Parametres!$B$66),0)</f>
         <v>75</v>
       </c>
-      <c r="D13" s="93" t="n">
+      <c r="D13" s="94" t="n">
         <f aca="false">C13*4.345</f>
         <v>325.875</v>
       </c>
@@ -5575,17 +5579,17 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="96" t="s">
         <v>633</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>634</v>
       </c>
-      <c r="C14" s="104" t="n">
+      <c r="C14" s="105" t="n">
         <f aca="false">ROUND($B$8/4.345*(Parametres!$B$70+Parametres!$B$71),1)</f>
         <v>1.4</v>
       </c>
-      <c r="D14" s="93" t="n">
+      <c r="D14" s="94" t="n">
         <f aca="false">C14*4.345</f>
         <v>6.083</v>
       </c>
@@ -5629,7 +5633,7 @@
       <c r="D19" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="E19" s="93" t="n">
+      <c r="E19" s="94" t="n">
         <f aca="false">C19/$C$12</f>
         <v>0.909090909090909</v>
       </c>
@@ -5648,7 +5652,7 @@
       <c r="D20" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="E20" s="93" t="n">
+      <c r="E20" s="94" t="n">
         <f aca="false">C20/$C$13</f>
         <v>0.533333333333333</v>
       </c>
@@ -5667,7 +5671,7 @@
       <c r="D21" s="8" t="s">
         <v>646</v>
       </c>
-      <c r="E21" s="93" t="n">
+      <c r="E21" s="94" t="n">
         <f aca="false">C21/$C$13</f>
         <v>1.77333333333333</v>
       </c>
@@ -5686,7 +5690,7 @@
       <c r="D22" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="E22" s="93" t="n">
+      <c r="E22" s="94" t="n">
         <f aca="false">C22/$C$13</f>
         <v>7.94666666666667</v>
       </c>
@@ -5705,7 +5709,7 @@
       <c r="D23" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="E23" s="93" t="n">
+      <c r="E23" s="94" t="n">
         <f aca="false">C23/$C$14</f>
         <v>3.57142857142857</v>
       </c>
@@ -5724,7 +5728,7 @@
       <c r="D24" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="E24" s="93" t="n">
+      <c r="E24" s="94" t="n">
         <f aca="false">C24/$C$14</f>
         <v>102.142857142857</v>
       </c>
@@ -5736,13 +5740,13 @@
       <c r="B25" s="36" t="s">
         <v>633</v>
       </c>
-      <c r="C25" s="105" t="n">
+      <c r="C25" s="106" t="n">
         <v>20</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="E25" s="93" t="n">
+      <c r="E25" s="94" t="n">
         <f aca="false">C25/$C$14</f>
         <v>14.2857142857143</v>
       </c>
@@ -5844,7 +5848,7 @@
       <c r="A6" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="B6" s="106" t="n">
+      <c r="B6" s="107" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -5879,7 +5883,7 @@
       <c r="A10" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="59" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5940,11 +5944,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A13-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>640</v>
       </c>
-      <c r="C13" s="56" t="n">
+      <c r="C13" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D13" s="56" t="n">
+      <c r="D13" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A13,1+Parametres!$B$48)</f>
         <v>1.02</v>
       </c>
@@ -5956,7 +5960,7 @@
         <f aca="false">E13</f>
         <v>694</v>
       </c>
-      <c r="G13" s="107" t="n">
+      <c r="G13" s="108" t="n">
         <f aca="false">MATCH(F13,Progression!$C$5:$C$54,1)</f>
         <v>4</v>
       </c>
@@ -5964,7 +5968,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G13)</f>
         <v>9</v>
       </c>
-      <c r="I13" s="51" t="n">
+      <c r="I13" s="52" t="n">
         <f aca="false">IF(G13&lt;Donjon!$B$42,0,MATCH(G13,Donjon!$B$42:$B$53,1))</f>
         <v>0</v>
       </c>
@@ -5988,11 +5992,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A14-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>643</v>
       </c>
-      <c r="C14" s="108" t="n">
+      <c r="C14" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D14" s="108" t="n">
+      <c r="D14" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A14,1+Parametres!$B$48)</f>
         <v>1.04</v>
       </c>
@@ -6004,7 +6008,7 @@
         <f aca="false">F13+E14</f>
         <v>1405</v>
       </c>
-      <c r="G14" s="109" t="n">
+      <c r="G14" s="110" t="n">
         <f aca="false">MATCH(F14,Progression!$C$5:$C$54,1)</f>
         <v>5</v>
       </c>
@@ -6012,7 +6016,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G14)</f>
         <v>13</v>
       </c>
-      <c r="I14" s="110" t="n">
+      <c r="I14" s="111" t="n">
         <f aca="false">IF(G14&lt;Donjon!$B$42,0,MATCH(G14,Donjon!$B$42:$B$53,1))</f>
         <v>0</v>
       </c>
@@ -6034,11 +6038,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A15-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>646</v>
       </c>
-      <c r="C15" s="56" t="n">
+      <c r="C15" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D15" s="56" t="n">
+      <c r="D15" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A15,1+Parametres!$B$48)</f>
         <v>1.06</v>
       </c>
@@ -6050,7 +6054,7 @@
         <f aca="false">F14+E15</f>
         <v>2133</v>
       </c>
-      <c r="G15" s="107" t="n">
+      <c r="G15" s="108" t="n">
         <f aca="false">MATCH(F15,Progression!$C$5:$C$54,1)</f>
         <v>6</v>
       </c>
@@ -6058,7 +6062,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G15)</f>
         <v>17</v>
       </c>
-      <c r="I15" s="51" t="n">
+      <c r="I15" s="52" t="n">
         <f aca="false">IF(G15&lt;Donjon!$B$42,0,MATCH(G15,Donjon!$B$42:$B$53,1))</f>
         <v>1</v>
       </c>
@@ -6080,11 +6084,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A16-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>650</v>
       </c>
-      <c r="C16" s="108" t="n">
+      <c r="C16" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D16" s="108" t="n">
+      <c r="D16" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A16,1+Parametres!$B$48)</f>
         <v>1.08</v>
       </c>
@@ -6096,7 +6100,7 @@
         <f aca="false">F15+E16</f>
         <v>2879</v>
       </c>
-      <c r="G16" s="109" t="n">
+      <c r="G16" s="110" t="n">
         <f aca="false">MATCH(F16,Progression!$C$5:$C$54,1)</f>
         <v>7</v>
       </c>
@@ -6104,7 +6108,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G16)</f>
         <v>21</v>
       </c>
-      <c r="I16" s="110" t="n">
+      <c r="I16" s="111" t="n">
         <f aca="false">IF(G16&lt;Donjon!$B$42,0,MATCH(G16,Donjon!$B$42:$B$53,1))</f>
         <v>2</v>
       </c>
@@ -6128,11 +6132,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A17-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>653</v>
       </c>
-      <c r="C17" s="56" t="n">
+      <c r="C17" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D17" s="56" t="n">
+      <c r="D17" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A17,1+Parametres!$B$48)</f>
         <v>1.1</v>
       </c>
@@ -6144,7 +6148,7 @@
         <f aca="false">F16+E17</f>
         <v>3643</v>
       </c>
-      <c r="G17" s="107" t="n">
+      <c r="G17" s="108" t="n">
         <f aca="false">MATCH(F17,Progression!$C$5:$C$54,1)</f>
         <v>8</v>
       </c>
@@ -6152,7 +6156,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G17)</f>
         <v>25</v>
       </c>
-      <c r="I17" s="51" t="n">
+      <c r="I17" s="52" t="n">
         <f aca="false">IF(G17&lt;Donjon!$B$42,0,MATCH(G17,Donjon!$B$42:$B$53,1))</f>
         <v>3</v>
       </c>
@@ -6174,11 +6178,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A18-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>656</v>
       </c>
-      <c r="C18" s="108" t="n">
+      <c r="C18" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D18" s="108" t="n">
+      <c r="D18" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A18,1+Parametres!$B$48)</f>
         <v>1.12</v>
       </c>
@@ -6190,7 +6194,7 @@
         <f aca="false">F17+E18</f>
         <v>4424</v>
       </c>
-      <c r="G18" s="109" t="n">
+      <c r="G18" s="110" t="n">
         <f aca="false">MATCH(F18,Progression!$C$5:$C$54,1)</f>
         <v>9</v>
       </c>
@@ -6198,7 +6202,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G18)</f>
         <v>29</v>
       </c>
-      <c r="I18" s="110" t="n">
+      <c r="I18" s="111" t="n">
         <f aca="false">IF(G18&lt;Donjon!$B$42,0,MATCH(G18,Donjon!$B$42:$B$53,1))</f>
         <v>3</v>
       </c>
@@ -6220,11 +6224,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A19-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>660</v>
       </c>
-      <c r="C19" s="56" t="n">
+      <c r="C19" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D19" s="56" t="n">
+      <c r="D19" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A19,1+Parametres!$B$48)</f>
         <v>1.14</v>
       </c>
@@ -6236,7 +6240,7 @@
         <f aca="false">F18+E19</f>
         <v>5224</v>
       </c>
-      <c r="G19" s="107" t="n">
+      <c r="G19" s="108" t="n">
         <f aca="false">MATCH(F19,Progression!$C$5:$C$54,1)</f>
         <v>9</v>
       </c>
@@ -6244,7 +6248,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G19)</f>
         <v>29</v>
       </c>
-      <c r="I19" s="51" t="n">
+      <c r="I19" s="52" t="n">
         <f aca="false">IF(G19&lt;Donjon!$B$42,0,MATCH(G19,Donjon!$B$42:$B$53,1))</f>
         <v>3</v>
       </c>
@@ -6266,11 +6270,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A20-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>663</v>
       </c>
-      <c r="C20" s="108" t="n">
+      <c r="C20" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D20" s="108" t="n">
+      <c r="D20" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A20,1+Parametres!$B$48)</f>
         <v>1.16</v>
       </c>
@@ -6282,7 +6286,7 @@
         <f aca="false">F19+E20</f>
         <v>6042</v>
       </c>
-      <c r="G20" s="109" t="n">
+      <c r="G20" s="110" t="n">
         <f aca="false">MATCH(F20,Progression!$C$5:$C$54,1)</f>
         <v>10</v>
       </c>
@@ -6290,7 +6294,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G20)</f>
         <v>34</v>
       </c>
-      <c r="I20" s="110" t="n">
+      <c r="I20" s="111" t="n">
         <f aca="false">IF(G20&lt;Donjon!$B$42,0,MATCH(G20,Donjon!$B$42:$B$53,1))</f>
         <v>4</v>
       </c>
@@ -6312,11 +6316,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A21-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>666</v>
       </c>
-      <c r="C21" s="56" t="n">
+      <c r="C21" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D21" s="56" t="n">
+      <c r="D21" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A21,1+Parametres!$B$48)</f>
         <v>1.18</v>
       </c>
@@ -6328,7 +6332,7 @@
         <f aca="false">F20+E21</f>
         <v>6878</v>
       </c>
-      <c r="G21" s="107" t="n">
+      <c r="G21" s="108" t="n">
         <f aca="false">MATCH(F21,Progression!$C$5:$C$54,1)</f>
         <v>10</v>
       </c>
@@ -6336,7 +6340,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G21)</f>
         <v>34</v>
       </c>
-      <c r="I21" s="51" t="n">
+      <c r="I21" s="52" t="n">
         <f aca="false">IF(G21&lt;Donjon!$B$42,0,MATCH(G21,Donjon!$B$42:$B$53,1))</f>
         <v>4</v>
       </c>
@@ -6358,11 +6362,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A22-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>670</v>
       </c>
-      <c r="C22" s="108" t="n">
+      <c r="C22" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D22" s="108" t="n">
+      <c r="D22" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A22,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6374,7 +6378,7 @@
         <f aca="false">F21+E22</f>
         <v>7733</v>
       </c>
-      <c r="G22" s="109" t="n">
+      <c r="G22" s="110" t="n">
         <f aca="false">MATCH(F22,Progression!$C$5:$C$54,1)</f>
         <v>11</v>
       </c>
@@ -6382,7 +6386,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G22)</f>
         <v>39</v>
       </c>
-      <c r="I22" s="110" t="n">
+      <c r="I22" s="111" t="n">
         <f aca="false">IF(G22&lt;Donjon!$B$42,0,MATCH(G22,Donjon!$B$42:$B$53,1))</f>
         <v>5</v>
       </c>
@@ -6404,11 +6408,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A23-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>673</v>
       </c>
-      <c r="C23" s="56" t="n">
+      <c r="C23" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D23" s="56" t="n">
+      <c r="D23" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A23,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6420,7 +6424,7 @@
         <f aca="false">F22+E23</f>
         <v>8592</v>
       </c>
-      <c r="G23" s="107" t="n">
+      <c r="G23" s="108" t="n">
         <f aca="false">MATCH(F23,Progression!$C$5:$C$54,1)</f>
         <v>11</v>
       </c>
@@ -6428,7 +6432,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G23)</f>
         <v>39</v>
       </c>
-      <c r="I23" s="51" t="n">
+      <c r="I23" s="52" t="n">
         <f aca="false">IF(G23&lt;Donjon!$B$42,0,MATCH(G23,Donjon!$B$42:$B$53,1))</f>
         <v>5</v>
       </c>
@@ -6450,11 +6454,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A24-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>677</v>
       </c>
-      <c r="C24" s="108" t="n">
+      <c r="C24" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D24" s="108" t="n">
+      <c r="D24" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A24,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6466,7 +6470,7 @@
         <f aca="false">F23+E24</f>
         <v>9456</v>
       </c>
-      <c r="G24" s="109" t="n">
+      <c r="G24" s="110" t="n">
         <f aca="false">MATCH(F24,Progression!$C$5:$C$54,1)</f>
         <v>12</v>
       </c>
@@ -6474,7 +6478,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G24)</f>
         <v>44</v>
       </c>
-      <c r="I24" s="110" t="n">
+      <c r="I24" s="111" t="n">
         <f aca="false">IF(G24&lt;Donjon!$B$42,0,MATCH(G24,Donjon!$B$42:$B$53,1))</f>
         <v>5</v>
       </c>
@@ -6496,11 +6500,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A25-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>680</v>
       </c>
-      <c r="C25" s="56" t="n">
+      <c r="C25" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D25" s="56" t="n">
+      <c r="D25" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A25,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6512,7 +6516,7 @@
         <f aca="false">F24+E25</f>
         <v>10324</v>
       </c>
-      <c r="G25" s="107" t="n">
+      <c r="G25" s="108" t="n">
         <f aca="false">MATCH(F25,Progression!$C$5:$C$54,1)</f>
         <v>12</v>
       </c>
@@ -6520,7 +6524,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G25)</f>
         <v>44</v>
       </c>
-      <c r="I25" s="51" t="n">
+      <c r="I25" s="52" t="n">
         <f aca="false">IF(G25&lt;Donjon!$B$42,0,MATCH(G25,Donjon!$B$42:$B$53,1))</f>
         <v>5</v>
       </c>
@@ -6544,11 +6548,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A26-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>684</v>
       </c>
-      <c r="C26" s="108" t="n">
+      <c r="C26" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D26" s="108" t="n">
+      <c r="D26" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A26,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6560,7 +6564,7 @@
         <f aca="false">F25+E26</f>
         <v>11197</v>
       </c>
-      <c r="G26" s="109" t="n">
+      <c r="G26" s="110" t="n">
         <f aca="false">MATCH(F26,Progression!$C$5:$C$54,1)</f>
         <v>13</v>
       </c>
@@ -6568,7 +6572,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G26)</f>
         <v>49</v>
       </c>
-      <c r="I26" s="110" t="n">
+      <c r="I26" s="111" t="n">
         <f aca="false">IF(G26&lt;Donjon!$B$42,0,MATCH(G26,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6590,11 +6594,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A27-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>687</v>
       </c>
-      <c r="C27" s="56" t="n">
+      <c r="C27" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D27" s="56" t="n">
+      <c r="D27" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A27,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6606,7 +6610,7 @@
         <f aca="false">F26+E27</f>
         <v>12074</v>
       </c>
-      <c r="G27" s="107" t="n">
+      <c r="G27" s="108" t="n">
         <f aca="false">MATCH(F27,Progression!$C$5:$C$54,1)</f>
         <v>13</v>
       </c>
@@ -6614,7 +6618,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G27)</f>
         <v>49</v>
       </c>
-      <c r="I27" s="51" t="n">
+      <c r="I27" s="52" t="n">
         <f aca="false">IF(G27&lt;Donjon!$B$42,0,MATCH(G27,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6636,11 +6640,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A28-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>691</v>
       </c>
-      <c r="C28" s="108" t="n">
+      <c r="C28" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D28" s="108" t="n">
+      <c r="D28" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A28,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6652,7 +6656,7 @@
         <f aca="false">F27+E28</f>
         <v>12956</v>
       </c>
-      <c r="G28" s="109" t="n">
+      <c r="G28" s="110" t="n">
         <f aca="false">MATCH(F28,Progression!$C$5:$C$54,1)</f>
         <v>13</v>
       </c>
@@ -6660,7 +6664,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G28)</f>
         <v>49</v>
       </c>
-      <c r="I28" s="110" t="n">
+      <c r="I28" s="111" t="n">
         <f aca="false">IF(G28&lt;Donjon!$B$42,0,MATCH(G28,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6682,11 +6686,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A29-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>694</v>
       </c>
-      <c r="C29" s="56" t="n">
+      <c r="C29" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D29" s="56" t="n">
+      <c r="D29" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A29,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6698,7 +6702,7 @@
         <f aca="false">F28+E29</f>
         <v>13842</v>
       </c>
-      <c r="G29" s="107" t="n">
+      <c r="G29" s="108" t="n">
         <f aca="false">MATCH(F29,Progression!$C$5:$C$54,1)</f>
         <v>14</v>
       </c>
@@ -6706,7 +6710,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G29)</f>
         <v>54</v>
       </c>
-      <c r="I29" s="51" t="n">
+      <c r="I29" s="52" t="n">
         <f aca="false">IF(G29&lt;Donjon!$B$42,0,MATCH(G29,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6728,11 +6732,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A30-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>698</v>
       </c>
-      <c r="C30" s="108" t="n">
+      <c r="C30" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D30" s="108" t="n">
+      <c r="D30" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A30,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6744,7 +6748,7 @@
         <f aca="false">F29+E30</f>
         <v>14733</v>
       </c>
-      <c r="G30" s="109" t="n">
+      <c r="G30" s="110" t="n">
         <f aca="false">MATCH(F30,Progression!$C$5:$C$54,1)</f>
         <v>14</v>
       </c>
@@ -6752,7 +6756,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G30)</f>
         <v>54</v>
       </c>
-      <c r="I30" s="110" t="n">
+      <c r="I30" s="111" t="n">
         <f aca="false">IF(G30&lt;Donjon!$B$42,0,MATCH(G30,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6774,11 +6778,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A31-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>702</v>
       </c>
-      <c r="C31" s="56" t="n">
+      <c r="C31" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D31" s="56" t="n">
+      <c r="D31" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A31,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6790,7 +6794,7 @@
         <f aca="false">F30+E31</f>
         <v>15629</v>
       </c>
-      <c r="G31" s="107" t="n">
+      <c r="G31" s="108" t="n">
         <f aca="false">MATCH(F31,Progression!$C$5:$C$54,1)</f>
         <v>14</v>
       </c>
@@ -6798,7 +6802,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G31)</f>
         <v>54</v>
       </c>
-      <c r="I31" s="51" t="n">
+      <c r="I31" s="52" t="n">
         <f aca="false">IF(G31&lt;Donjon!$B$42,0,MATCH(G31,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6820,11 +6824,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A32-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>705</v>
       </c>
-      <c r="C32" s="108" t="n">
+      <c r="C32" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D32" s="108" t="n">
+      <c r="D32" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A32,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6836,7 +6840,7 @@
         <f aca="false">F31+E32</f>
         <v>16529</v>
       </c>
-      <c r="G32" s="109" t="n">
+      <c r="G32" s="110" t="n">
         <f aca="false">MATCH(F32,Progression!$C$5:$C$54,1)</f>
         <v>15</v>
       </c>
@@ -6844,7 +6848,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G32)</f>
         <v>60</v>
       </c>
-      <c r="I32" s="110" t="n">
+      <c r="I32" s="111" t="n">
         <f aca="false">IF(G32&lt;Donjon!$B$42,0,MATCH(G32,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6866,11 +6870,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A33-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>709</v>
       </c>
-      <c r="C33" s="56" t="n">
+      <c r="C33" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D33" s="56" t="n">
+      <c r="D33" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A33,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6882,7 +6886,7 @@
         <f aca="false">F32+E33</f>
         <v>17434</v>
       </c>
-      <c r="G33" s="107" t="n">
+      <c r="G33" s="108" t="n">
         <f aca="false">MATCH(F33,Progression!$C$5:$C$54,1)</f>
         <v>15</v>
       </c>
@@ -6890,7 +6894,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G33)</f>
         <v>60</v>
       </c>
-      <c r="I33" s="51" t="n">
+      <c r="I33" s="52" t="n">
         <f aca="false">IF(G33&lt;Donjon!$B$42,0,MATCH(G33,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6912,11 +6916,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A34-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>713</v>
       </c>
-      <c r="C34" s="108" t="n">
+      <c r="C34" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D34" s="108" t="n">
+      <c r="D34" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A34,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6928,7 +6932,7 @@
         <f aca="false">F33+E34</f>
         <v>18344</v>
       </c>
-      <c r="G34" s="109" t="n">
+      <c r="G34" s="110" t="n">
         <f aca="false">MATCH(F34,Progression!$C$5:$C$54,1)</f>
         <v>15</v>
       </c>
@@ -6936,7 +6940,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G34)</f>
         <v>60</v>
       </c>
-      <c r="I34" s="110" t="n">
+      <c r="I34" s="111" t="n">
         <f aca="false">IF(G34&lt;Donjon!$B$42,0,MATCH(G34,Donjon!$B$42:$B$53,1))</f>
         <v>6</v>
       </c>
@@ -6958,11 +6962,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A35-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>717</v>
       </c>
-      <c r="C35" s="56" t="n">
+      <c r="C35" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D35" s="56" t="n">
+      <c r="D35" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A35,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -6974,7 +6978,7 @@
         <f aca="false">F34+E35</f>
         <v>19259</v>
       </c>
-      <c r="G35" s="107" t="n">
+      <c r="G35" s="108" t="n">
         <f aca="false">MATCH(F35,Progression!$C$5:$C$54,1)</f>
         <v>16</v>
       </c>
@@ -6982,7 +6986,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G35)</f>
         <v>66</v>
       </c>
-      <c r="I35" s="51" t="n">
+      <c r="I35" s="52" t="n">
         <f aca="false">IF(G35&lt;Donjon!$B$42,0,MATCH(G35,Donjon!$B$42:$B$53,1))</f>
         <v>7</v>
       </c>
@@ -7004,11 +7008,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A36-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>720</v>
       </c>
-      <c r="C36" s="108" t="n">
+      <c r="C36" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D36" s="108" t="n">
+      <c r="D36" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A36,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7020,7 +7024,7 @@
         <f aca="false">F35+E36</f>
         <v>20178</v>
       </c>
-      <c r="G36" s="109" t="n">
+      <c r="G36" s="110" t="n">
         <f aca="false">MATCH(F36,Progression!$C$5:$C$54,1)</f>
         <v>16</v>
       </c>
@@ -7028,7 +7032,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G36)</f>
         <v>66</v>
       </c>
-      <c r="I36" s="110" t="n">
+      <c r="I36" s="111" t="n">
         <f aca="false">IF(G36&lt;Donjon!$B$42,0,MATCH(G36,Donjon!$B$42:$B$53,1))</f>
         <v>7</v>
       </c>
@@ -7050,11 +7054,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A37-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>724</v>
       </c>
-      <c r="C37" s="56" t="n">
+      <c r="C37" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D37" s="56" t="n">
+      <c r="D37" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A37,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7066,7 +7070,7 @@
         <f aca="false">F36+E37</f>
         <v>21102</v>
       </c>
-      <c r="G37" s="107" t="n">
+      <c r="G37" s="108" t="n">
         <f aca="false">MATCH(F37,Progression!$C$5:$C$54,1)</f>
         <v>16</v>
       </c>
@@ -7074,7 +7078,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G37)</f>
         <v>66</v>
       </c>
-      <c r="I37" s="51" t="n">
+      <c r="I37" s="52" t="n">
         <f aca="false">IF(G37&lt;Donjon!$B$42,0,MATCH(G37,Donjon!$B$42:$B$53,1))</f>
         <v>7</v>
       </c>
@@ -7096,11 +7100,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A38-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>728</v>
       </c>
-      <c r="C38" s="108" t="n">
+      <c r="C38" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D38" s="108" t="n">
+      <c r="D38" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A38,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7112,7 +7116,7 @@
         <f aca="false">F37+E38</f>
         <v>22031</v>
       </c>
-      <c r="G38" s="109" t="n">
+      <c r="G38" s="110" t="n">
         <f aca="false">MATCH(F38,Progression!$C$5:$C$54,1)</f>
         <v>16</v>
       </c>
@@ -7120,7 +7124,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G38)</f>
         <v>66</v>
       </c>
-      <c r="I38" s="110" t="n">
+      <c r="I38" s="111" t="n">
         <f aca="false">IF(G38&lt;Donjon!$B$42,0,MATCH(G38,Donjon!$B$42:$B$53,1))</f>
         <v>7</v>
       </c>
@@ -7144,11 +7148,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A39-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>732</v>
       </c>
-      <c r="C39" s="56" t="n">
+      <c r="C39" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D39" s="56" t="n">
+      <c r="D39" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A39,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7160,7 +7164,7 @@
         <f aca="false">F38+E39</f>
         <v>22965</v>
       </c>
-      <c r="G39" s="107" t="n">
+      <c r="G39" s="108" t="n">
         <f aca="false">MATCH(F39,Progression!$C$5:$C$54,1)</f>
         <v>17</v>
       </c>
@@ -7168,7 +7172,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G39)</f>
         <v>72</v>
       </c>
-      <c r="I39" s="51" t="n">
+      <c r="I39" s="52" t="n">
         <f aca="false">IF(G39&lt;Donjon!$B$42,0,MATCH(G39,Donjon!$B$42:$B$53,1))</f>
         <v>7</v>
       </c>
@@ -7190,11 +7194,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A40-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>736</v>
       </c>
-      <c r="C40" s="108" t="n">
+      <c r="C40" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D40" s="108" t="n">
+      <c r="D40" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A40,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7206,7 +7210,7 @@
         <f aca="false">F39+E40</f>
         <v>23904</v>
       </c>
-      <c r="G40" s="109" t="n">
+      <c r="G40" s="110" t="n">
         <f aca="false">MATCH(F40,Progression!$C$5:$C$54,1)</f>
         <v>17</v>
       </c>
@@ -7214,7 +7218,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G40)</f>
         <v>72</v>
       </c>
-      <c r="I40" s="110" t="n">
+      <c r="I40" s="111" t="n">
         <f aca="false">IF(G40&lt;Donjon!$B$42,0,MATCH(G40,Donjon!$B$42:$B$53,1))</f>
         <v>7</v>
       </c>
@@ -7236,11 +7240,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A41-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>740</v>
       </c>
-      <c r="C41" s="56" t="n">
+      <c r="C41" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D41" s="56" t="n">
+      <c r="D41" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A41,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7252,7 +7256,7 @@
         <f aca="false">F40+E41</f>
         <v>24848</v>
       </c>
-      <c r="G41" s="107" t="n">
+      <c r="G41" s="108" t="n">
         <f aca="false">MATCH(F41,Progression!$C$5:$C$54,1)</f>
         <v>17</v>
       </c>
@@ -7260,7 +7264,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G41)</f>
         <v>72</v>
       </c>
-      <c r="I41" s="51" t="n">
+      <c r="I41" s="52" t="n">
         <f aca="false">IF(G41&lt;Donjon!$B$42,0,MATCH(G41,Donjon!$B$42:$B$53,1))</f>
         <v>7</v>
       </c>
@@ -7282,11 +7286,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A42-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>744</v>
       </c>
-      <c r="C42" s="108" t="n">
+      <c r="C42" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D42" s="108" t="n">
+      <c r="D42" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A42,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7298,7 +7302,7 @@
         <f aca="false">F41+E42</f>
         <v>25797</v>
       </c>
-      <c r="G42" s="109" t="n">
+      <c r="G42" s="110" t="n">
         <f aca="false">MATCH(F42,Progression!$C$5:$C$54,1)</f>
         <v>18</v>
       </c>
@@ -7306,7 +7310,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G42)</f>
         <v>78</v>
       </c>
-      <c r="I42" s="110" t="n">
+      <c r="I42" s="111" t="n">
         <f aca="false">IF(G42&lt;Donjon!$B$42,0,MATCH(G42,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7328,11 +7332,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A43-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>748</v>
       </c>
-      <c r="C43" s="56" t="n">
+      <c r="C43" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D43" s="56" t="n">
+      <c r="D43" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A43,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7344,7 +7348,7 @@
         <f aca="false">F42+E43</f>
         <v>26751</v>
       </c>
-      <c r="G43" s="107" t="n">
+      <c r="G43" s="108" t="n">
         <f aca="false">MATCH(F43,Progression!$C$5:$C$54,1)</f>
         <v>18</v>
       </c>
@@ -7352,7 +7356,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G43)</f>
         <v>78</v>
       </c>
-      <c r="I43" s="51" t="n">
+      <c r="I43" s="52" t="n">
         <f aca="false">IF(G43&lt;Donjon!$B$42,0,MATCH(G43,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7374,11 +7378,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A44-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>752</v>
       </c>
-      <c r="C44" s="108" t="n">
+      <c r="C44" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D44" s="108" t="n">
+      <c r="D44" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A44,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7390,7 +7394,7 @@
         <f aca="false">F43+E44</f>
         <v>27711</v>
       </c>
-      <c r="G44" s="109" t="n">
+      <c r="G44" s="110" t="n">
         <f aca="false">MATCH(F44,Progression!$C$5:$C$54,1)</f>
         <v>18</v>
       </c>
@@ -7398,7 +7402,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G44)</f>
         <v>78</v>
       </c>
-      <c r="I44" s="110" t="n">
+      <c r="I44" s="111" t="n">
         <f aca="false">IF(G44&lt;Donjon!$B$42,0,MATCH(G44,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7420,11 +7424,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A45-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>756</v>
       </c>
-      <c r="C45" s="56" t="n">
+      <c r="C45" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D45" s="56" t="n">
+      <c r="D45" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A45,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7436,7 +7440,7 @@
         <f aca="false">F44+E45</f>
         <v>28676</v>
       </c>
-      <c r="G45" s="107" t="n">
+      <c r="G45" s="108" t="n">
         <f aca="false">MATCH(F45,Progression!$C$5:$C$54,1)</f>
         <v>18</v>
       </c>
@@ -7444,7 +7448,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G45)</f>
         <v>78</v>
       </c>
-      <c r="I45" s="51" t="n">
+      <c r="I45" s="52" t="n">
         <f aca="false">IF(G45&lt;Donjon!$B$42,0,MATCH(G45,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7466,11 +7470,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A46-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>760</v>
       </c>
-      <c r="C46" s="108" t="n">
+      <c r="C46" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D46" s="108" t="n">
+      <c r="D46" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A46,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7482,7 +7486,7 @@
         <f aca="false">F45+E46</f>
         <v>29646</v>
       </c>
-      <c r="G46" s="109" t="n">
+      <c r="G46" s="110" t="n">
         <f aca="false">MATCH(F46,Progression!$C$5:$C$54,1)</f>
         <v>19</v>
       </c>
@@ -7490,7 +7494,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G46)</f>
         <v>84</v>
       </c>
-      <c r="I46" s="110" t="n">
+      <c r="I46" s="111" t="n">
         <f aca="false">IF(G46&lt;Donjon!$B$42,0,MATCH(G46,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7512,11 +7516,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A47-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>764</v>
       </c>
-      <c r="C47" s="56" t="n">
+      <c r="C47" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D47" s="56" t="n">
+      <c r="D47" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A47,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7528,7 +7532,7 @@
         <f aca="false">F46+E47</f>
         <v>30621</v>
       </c>
-      <c r="G47" s="107" t="n">
+      <c r="G47" s="108" t="n">
         <f aca="false">MATCH(F47,Progression!$C$5:$C$54,1)</f>
         <v>19</v>
       </c>
@@ -7536,7 +7540,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G47)</f>
         <v>84</v>
       </c>
-      <c r="I47" s="51" t="n">
+      <c r="I47" s="52" t="n">
         <f aca="false">IF(G47&lt;Donjon!$B$42,0,MATCH(G47,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7558,11 +7562,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A48-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>769</v>
       </c>
-      <c r="C48" s="108" t="n">
+      <c r="C48" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D48" s="108" t="n">
+      <c r="D48" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A48,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7574,7 +7578,7 @@
         <f aca="false">F47+E48</f>
         <v>31602</v>
       </c>
-      <c r="G48" s="109" t="n">
+      <c r="G48" s="110" t="n">
         <f aca="false">MATCH(F48,Progression!$C$5:$C$54,1)</f>
         <v>19</v>
       </c>
@@ -7582,7 +7586,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G48)</f>
         <v>84</v>
       </c>
-      <c r="I48" s="110" t="n">
+      <c r="I48" s="111" t="n">
         <f aca="false">IF(G48&lt;Donjon!$B$42,0,MATCH(G48,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7604,11 +7608,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A49-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>773</v>
       </c>
-      <c r="C49" s="56" t="n">
+      <c r="C49" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D49" s="56" t="n">
+      <c r="D49" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A49,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7620,7 +7624,7 @@
         <f aca="false">F48+E49</f>
         <v>32588</v>
       </c>
-      <c r="G49" s="107" t="n">
+      <c r="G49" s="108" t="n">
         <f aca="false">MATCH(F49,Progression!$C$5:$C$54,1)</f>
         <v>19</v>
       </c>
@@ -7628,7 +7632,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G49)</f>
         <v>84</v>
       </c>
-      <c r="I49" s="51" t="n">
+      <c r="I49" s="52" t="n">
         <f aca="false">IF(G49&lt;Donjon!$B$42,0,MATCH(G49,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7650,11 +7654,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A50-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>777</v>
       </c>
-      <c r="C50" s="108" t="n">
+      <c r="C50" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D50" s="108" t="n">
+      <c r="D50" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A50,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7666,7 +7670,7 @@
         <f aca="false">F49+E50</f>
         <v>33579</v>
       </c>
-      <c r="G50" s="109" t="n">
+      <c r="G50" s="110" t="n">
         <f aca="false">MATCH(F50,Progression!$C$5:$C$54,1)</f>
         <v>20</v>
       </c>
@@ -7674,7 +7678,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G50)</f>
         <v>91</v>
       </c>
-      <c r="I50" s="110" t="n">
+      <c r="I50" s="111" t="n">
         <f aca="false">IF(G50&lt;Donjon!$B$42,0,MATCH(G50,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7696,11 +7700,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A51-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>781</v>
       </c>
-      <c r="C51" s="56" t="n">
+      <c r="C51" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D51" s="56" t="n">
+      <c r="D51" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A51,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7712,7 +7716,7 @@
         <f aca="false">F50+E51</f>
         <v>34576</v>
       </c>
-      <c r="G51" s="107" t="n">
+      <c r="G51" s="108" t="n">
         <f aca="false">MATCH(F51,Progression!$C$5:$C$54,1)</f>
         <v>20</v>
       </c>
@@ -7720,7 +7724,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G51)</f>
         <v>91</v>
       </c>
-      <c r="I51" s="51" t="n">
+      <c r="I51" s="52" t="n">
         <f aca="false">IF(G51&lt;Donjon!$B$42,0,MATCH(G51,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7744,11 +7748,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A52-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>786</v>
       </c>
-      <c r="C52" s="108" t="n">
+      <c r="C52" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D52" s="108" t="n">
+      <c r="D52" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A52,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7760,7 +7764,7 @@
         <f aca="false">F51+E52</f>
         <v>35579</v>
       </c>
-      <c r="G52" s="109" t="n">
+      <c r="G52" s="110" t="n">
         <f aca="false">MATCH(F52,Progression!$C$5:$C$54,1)</f>
         <v>20</v>
       </c>
@@ -7768,7 +7772,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G52)</f>
         <v>91</v>
       </c>
-      <c r="I52" s="110" t="n">
+      <c r="I52" s="111" t="n">
         <f aca="false">IF(G52&lt;Donjon!$B$42,0,MATCH(G52,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7790,11 +7794,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A53-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>790</v>
       </c>
-      <c r="C53" s="56" t="n">
+      <c r="C53" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D53" s="56" t="n">
+      <c r="D53" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A53,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7806,7 +7810,7 @@
         <f aca="false">F52+E53</f>
         <v>36587</v>
       </c>
-      <c r="G53" s="107" t="n">
+      <c r="G53" s="108" t="n">
         <f aca="false">MATCH(F53,Progression!$C$5:$C$54,1)</f>
         <v>20</v>
       </c>
@@ -7814,7 +7818,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G53)</f>
         <v>91</v>
       </c>
-      <c r="I53" s="51" t="n">
+      <c r="I53" s="52" t="n">
         <f aca="false">IF(G53&lt;Donjon!$B$42,0,MATCH(G53,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7836,11 +7840,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A54-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>795</v>
       </c>
-      <c r="C54" s="108" t="n">
+      <c r="C54" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D54" s="108" t="n">
+      <c r="D54" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A54,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7852,7 +7856,7 @@
         <f aca="false">F53+E54</f>
         <v>37601</v>
       </c>
-      <c r="G54" s="109" t="n">
+      <c r="G54" s="110" t="n">
         <f aca="false">MATCH(F54,Progression!$C$5:$C$54,1)</f>
         <v>20</v>
       </c>
@@ -7860,7 +7864,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G54)</f>
         <v>91</v>
       </c>
-      <c r="I54" s="110" t="n">
+      <c r="I54" s="111" t="n">
         <f aca="false">IF(G54&lt;Donjon!$B$42,0,MATCH(G54,Donjon!$B$42:$B$53,1))</f>
         <v>8</v>
       </c>
@@ -7882,11 +7886,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A55-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>799</v>
       </c>
-      <c r="C55" s="56" t="n">
+      <c r="C55" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D55" s="56" t="n">
+      <c r="D55" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A55,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7898,7 +7902,7 @@
         <f aca="false">F54+E55</f>
         <v>38620</v>
       </c>
-      <c r="G55" s="107" t="n">
+      <c r="G55" s="108" t="n">
         <f aca="false">MATCH(F55,Progression!$C$5:$C$54,1)</f>
         <v>21</v>
       </c>
@@ -7906,7 +7910,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G55)</f>
         <v>98</v>
       </c>
-      <c r="I55" s="51" t="n">
+      <c r="I55" s="52" t="n">
         <f aca="false">IF(G55&lt;Donjon!$B$42,0,MATCH(G55,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -7928,11 +7932,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A56-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>803</v>
       </c>
-      <c r="C56" s="108" t="n">
+      <c r="C56" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D56" s="108" t="n">
+      <c r="D56" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A56,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7944,7 +7948,7 @@
         <f aca="false">F55+E56</f>
         <v>39645</v>
       </c>
-      <c r="G56" s="109" t="n">
+      <c r="G56" s="110" t="n">
         <f aca="false">MATCH(F56,Progression!$C$5:$C$54,1)</f>
         <v>21</v>
       </c>
@@ -7952,7 +7956,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G56)</f>
         <v>98</v>
       </c>
-      <c r="I56" s="110" t="n">
+      <c r="I56" s="111" t="n">
         <f aca="false">IF(G56&lt;Donjon!$B$42,0,MATCH(G56,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -7974,11 +7978,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A57-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>808</v>
       </c>
-      <c r="C57" s="56" t="n">
+      <c r="C57" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D57" s="56" t="n">
+      <c r="D57" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A57,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -7990,7 +7994,7 @@
         <f aca="false">F56+E57</f>
         <v>40676</v>
       </c>
-      <c r="G57" s="107" t="n">
+      <c r="G57" s="108" t="n">
         <f aca="false">MATCH(F57,Progression!$C$5:$C$54,1)</f>
         <v>21</v>
       </c>
@@ -7998,7 +8002,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G57)</f>
         <v>98</v>
       </c>
-      <c r="I57" s="51" t="n">
+      <c r="I57" s="52" t="n">
         <f aca="false">IF(G57&lt;Donjon!$B$42,0,MATCH(G57,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -8020,11 +8024,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A58-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>813</v>
       </c>
-      <c r="C58" s="108" t="n">
+      <c r="C58" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D58" s="108" t="n">
+      <c r="D58" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A58,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -8036,7 +8040,7 @@
         <f aca="false">F57+E58</f>
         <v>41713</v>
       </c>
-      <c r="G58" s="109" t="n">
+      <c r="G58" s="110" t="n">
         <f aca="false">MATCH(F58,Progression!$C$5:$C$54,1)</f>
         <v>21</v>
       </c>
@@ -8044,7 +8048,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G58)</f>
         <v>98</v>
       </c>
-      <c r="I58" s="110" t="n">
+      <c r="I58" s="111" t="n">
         <f aca="false">IF(G58&lt;Donjon!$B$42,0,MATCH(G58,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -8066,11 +8070,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A59-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>817</v>
       </c>
-      <c r="C59" s="56" t="n">
+      <c r="C59" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D59" s="56" t="n">
+      <c r="D59" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A59,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -8082,7 +8086,7 @@
         <f aca="false">F58+E59</f>
         <v>42755</v>
       </c>
-      <c r="G59" s="107" t="n">
+      <c r="G59" s="108" t="n">
         <f aca="false">MATCH(F59,Progression!$C$5:$C$54,1)</f>
         <v>21</v>
       </c>
@@ -8090,7 +8094,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G59)</f>
         <v>98</v>
       </c>
-      <c r="I59" s="51" t="n">
+      <c r="I59" s="52" t="n">
         <f aca="false">IF(G59&lt;Donjon!$B$42,0,MATCH(G59,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -8112,11 +8116,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A60-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>822</v>
       </c>
-      <c r="C60" s="108" t="n">
+      <c r="C60" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D60" s="108" t="n">
+      <c r="D60" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A60,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -8128,7 +8132,7 @@
         <f aca="false">F59+E60</f>
         <v>43804</v>
       </c>
-      <c r="G60" s="109" t="n">
+      <c r="G60" s="110" t="n">
         <f aca="false">MATCH(F60,Progression!$C$5:$C$54,1)</f>
         <v>22</v>
       </c>
@@ -8136,7 +8140,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G60)</f>
         <v>105</v>
       </c>
-      <c r="I60" s="110" t="n">
+      <c r="I60" s="111" t="n">
         <f aca="false">IF(G60&lt;Donjon!$B$42,0,MATCH(G60,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -8158,11 +8162,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A61-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>826</v>
       </c>
-      <c r="C61" s="56" t="n">
+      <c r="C61" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D61" s="56" t="n">
+      <c r="D61" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A61,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -8174,7 +8178,7 @@
         <f aca="false">F60+E61</f>
         <v>44858</v>
       </c>
-      <c r="G61" s="107" t="n">
+      <c r="G61" s="108" t="n">
         <f aca="false">MATCH(F61,Progression!$C$5:$C$54,1)</f>
         <v>22</v>
       </c>
@@ -8182,7 +8186,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G61)</f>
         <v>105</v>
       </c>
-      <c r="I61" s="51" t="n">
+      <c r="I61" s="52" t="n">
         <f aca="false">IF(G61&lt;Donjon!$B$42,0,MATCH(G61,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -8204,11 +8208,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A62-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>831</v>
       </c>
-      <c r="C62" s="108" t="n">
+      <c r="C62" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D62" s="108" t="n">
+      <c r="D62" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A62,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -8220,7 +8224,7 @@
         <f aca="false">F61+E62</f>
         <v>45918</v>
       </c>
-      <c r="G62" s="109" t="n">
+      <c r="G62" s="110" t="n">
         <f aca="false">MATCH(F62,Progression!$C$5:$C$54,1)</f>
         <v>22</v>
       </c>
@@ -8228,7 +8232,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G62)</f>
         <v>105</v>
       </c>
-      <c r="I62" s="110" t="n">
+      <c r="I62" s="111" t="n">
         <f aca="false">IF(G62&lt;Donjon!$B$42,0,MATCH(G62,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -8250,11 +8254,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A63-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>836</v>
       </c>
-      <c r="C63" s="56" t="n">
+      <c r="C63" s="57" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D63" s="56" t="n">
+      <c r="D63" s="57" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A63,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -8266,7 +8270,7 @@
         <f aca="false">F62+E63</f>
         <v>46985</v>
       </c>
-      <c r="G63" s="107" t="n">
+      <c r="G63" s="108" t="n">
         <f aca="false">MATCH(F63,Progression!$C$5:$C$54,1)</f>
         <v>22</v>
       </c>
@@ -8274,7 +8278,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G63)</f>
         <v>105</v>
       </c>
-      <c r="I63" s="51" t="n">
+      <c r="I63" s="52" t="n">
         <f aca="false">IF(G63&lt;Donjon!$B$42,0,MATCH(G63,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -8296,11 +8300,11 @@
         <f aca="false">ROUND($B$5*(Parametres!$B$5+$B$6*MIN(2,(1+$B$11)^(A64-1))/Parametres!$B$6+$B$7*Parametres!$B$7),0)</f>
         <v>841</v>
       </c>
-      <c r="C64" s="108" t="n">
+      <c r="C64" s="109" t="n">
         <f aca="false">1+$B$8*(Parametres!$B$28+Parametres!$B$29+Parametres!$B$30)</f>
         <v>1.085</v>
       </c>
-      <c r="D64" s="108" t="n">
+      <c r="D64" s="109" t="n">
         <f aca="false">MIN(1+Parametres!$B$47*A64,1+Parametres!$B$48)</f>
         <v>1.2</v>
       </c>
@@ -8312,7 +8316,7 @@
         <f aca="false">F63+E64</f>
         <v>48058</v>
       </c>
-      <c r="G64" s="109" t="n">
+      <c r="G64" s="110" t="n">
         <f aca="false">MATCH(F64,Progression!$C$5:$C$54,1)</f>
         <v>23</v>
       </c>
@@ -8320,7 +8324,7 @@
         <f aca="false">INDEX(Progression!$I$5:$I$54,G64)</f>
         <v>112</v>
       </c>
-      <c r="I64" s="110" t="n">
+      <c r="I64" s="111" t="n">
         <f aca="false">IF(G64&lt;Donjon!$B$42,0,MATCH(G64,Donjon!$B$42:$B$53,1))</f>
         <v>9</v>
       </c>
@@ -12443,8 +12447,9 @@
         <f aca="false">ROUND(Parametres!$B$5+B14/Parametres!$B$6+C14*Parametres!$B$7,0)</f>
         <v>150</v>
       </c>
-      <c r="E14" s="40" t="n">
-        <v>1.25</v>
+      <c r="E14" s="42" t="n">
+        <f aca="false">1+'Nutrition-Moral'!$C$9</f>
+        <v>1.17</v>
       </c>
       <c r="F14" s="40" t="n">
         <v>1</v>
@@ -12454,11 +12459,11 @@
       </c>
       <c r="H14" s="41" t="n">
         <f aca="false">ROUND(D14*E14*F14*G14,0)</f>
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="I14" s="23" t="n">
         <f aca="false">H14/Progression!$C$9</f>
-        <v>0.220916568742656</v>
+        <v>0.206815511163337</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12475,8 +12480,9 @@
         <f aca="false">ROUND(Parametres!$B$5+B15/Parametres!$B$6+C15*Parametres!$B$7,0)</f>
         <v>175</v>
       </c>
-      <c r="E15" s="40" t="n">
-        <v>1.25</v>
+      <c r="E15" s="42" t="n">
+        <f aca="false">1+'Nutrition-Moral'!$C$9</f>
+        <v>1.17</v>
       </c>
       <c r="F15" s="40" t="n">
         <v>1</v>
@@ -12486,11 +12492,11 @@
       </c>
       <c r="H15" s="41" t="n">
         <f aca="false">ROUND(D15*E15*F15*G15,0)</f>
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="I15" s="23" t="n">
         <f aca="false">H15/Progression!$C$9</f>
-        <v>0.257344300822562</v>
+        <v>0.240893066980024</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12507,8 +12513,9 @@
         <f aca="false">ROUND(Parametres!$B$5+B16/Parametres!$B$6+C16*Parametres!$B$7,0)</f>
         <v>250</v>
       </c>
-      <c r="E16" s="40" t="n">
-        <v>1.25</v>
+      <c r="E16" s="42" t="n">
+        <f aca="false">'Nutrition-Moral'!$D$32</f>
+        <v>1.32</v>
       </c>
       <c r="F16" s="40" t="n">
         <v>1</v>
@@ -12518,11 +12525,11 @@
       </c>
       <c r="H16" s="41" t="n">
         <f aca="false">ROUND(D16*E16*F16*G16,0)</f>
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="I16" s="23" t="n">
         <f aca="false">H16/Progression!$C$9</f>
-        <v>0.440658049353702</v>
+        <v>0.465334900117509</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12719,7 +12726,7 @@
       <c r="B6" s="36" t="s">
         <v>352</v>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="43" t="n">
         <f aca="false">Parametres!$B$28</f>
         <v>0.05</v>
       </c>
@@ -12734,7 +12741,7 @@
       <c r="B7" s="36" t="s">
         <v>355</v>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="43" t="n">
         <f aca="false">Parametres!$B$29</f>
         <v>0.08</v>
       </c>
@@ -12749,7 +12756,7 @@
       <c r="B8" s="36" t="s">
         <v>357</v>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="43" t="n">
         <f aca="false">Parametres!$B$30</f>
         <v>0.04</v>
       </c>
@@ -12758,10 +12765,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="44" t="s">
         <v>358</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="45" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>0.17</v>
       </c>
@@ -12801,14 +12808,14 @@
       <c r="C13" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D13" s="43" t="n">
         <f aca="false">Parametres!$B$28+Parametres!$B$29+Parametres!$B$30</f>
         <v>0.17</v>
       </c>
       <c r="E13" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="46" t="s">
         <v>364</v>
       </c>
     </row>
@@ -12822,14 +12829,14 @@
       <c r="C14" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="D14" s="42" t="n">
+      <c r="D14" s="43" t="n">
         <f aca="false">Parametres!$B$28+Parametres!$B$29+0</f>
         <v>0.13</v>
       </c>
       <c r="E14" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="46" t="s">
         <v>364</v>
       </c>
     </row>
@@ -12843,14 +12850,14 @@
       <c r="C15" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="D15" s="42" t="n">
+      <c r="D15" s="43" t="n">
         <f aca="false">Parametres!$B$28+0+Parametres!$B$30</f>
         <v>0.09</v>
       </c>
       <c r="E15" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="46" t="s">
         <v>364</v>
       </c>
     </row>
@@ -12864,14 +12871,14 @@
       <c r="C16" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="D16" s="42" t="n">
+      <c r="D16" s="43" t="n">
         <f aca="false">Parametres!$B$28+0+0</f>
         <v>0.05</v>
       </c>
       <c r="E16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="47" t="s">
         <v>366</v>
       </c>
     </row>
@@ -12885,14 +12892,14 @@
       <c r="C17" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="D17" s="42" t="n">
+      <c r="D17" s="43" t="n">
         <f aca="false">0+Parametres!$B$29+Parametres!$B$30</f>
         <v>0.12</v>
       </c>
       <c r="E17" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="45" t="s">
+      <c r="F17" s="46" t="s">
         <v>364</v>
       </c>
     </row>
@@ -12906,14 +12913,14 @@
       <c r="C18" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="D18" s="42" t="n">
+      <c r="D18" s="43" t="n">
         <f aca="false">0+Parametres!$B$29+0</f>
         <v>0.08</v>
       </c>
       <c r="E18" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="47" t="s">
         <v>366</v>
       </c>
     </row>
@@ -12927,35 +12934,35 @@
       <c r="C19" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="D19" s="42" t="n">
+      <c r="D19" s="43" t="n">
         <f aca="false">0+0+Parametres!$B$30</f>
         <v>0.04</v>
       </c>
       <c r="E19" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="46" t="s">
+      <c r="F19" s="47" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="48" t="s">
         <v>365</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="48" t="s">
         <v>365</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="48" t="s">
         <v>365</v>
       </c>
-      <c r="D20" s="48" t="n">
+      <c r="D20" s="49" t="n">
         <f aca="false">0+0+0</f>
         <v>0</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="49" t="s">
+      <c r="F20" s="50" t="s">
         <v>366</v>
       </c>
     </row>
@@ -12989,137 +12996,137 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="50" t="n">
+      <c r="A26" s="51" t="n">
         <v>0</v>
       </c>
       <c r="B26" s="23" t="n">
         <f aca="false">MIN(A26*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="51" t="n">
+      <c r="C26" s="52" t="n">
         <f aca="false">MIN(A26*Parametres!$B$33,Parametres!$B$34)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="52" t="n">
+      <c r="D26" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B26</f>
         <v>1.17</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="50" t="n">
+      <c r="A27" s="51" t="n">
         <v>1</v>
       </c>
       <c r="B27" s="23" t="n">
         <f aca="false">MIN(A27*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0.01</v>
       </c>
-      <c r="C27" s="51" t="n">
+      <c r="C27" s="52" t="n">
         <f aca="false">MIN(A27*Parametres!$B$33,Parametres!$B$34)</f>
         <v>2</v>
       </c>
-      <c r="D27" s="52" t="n">
+      <c r="D27" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B27</f>
         <v>1.18</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="n">
+      <c r="A28" s="51" t="n">
         <v>3</v>
       </c>
       <c r="B28" s="23" t="n">
         <f aca="false">MIN(A28*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0.03</v>
       </c>
-      <c r="C28" s="51" t="n">
+      <c r="C28" s="52" t="n">
         <f aca="false">MIN(A28*Parametres!$B$33,Parametres!$B$34)</f>
         <v>6</v>
       </c>
-      <c r="D28" s="52" t="n">
+      <c r="D28" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B28</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="50" t="n">
+      <c r="A29" s="51" t="n">
         <v>5</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">MIN(A29*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0.05</v>
       </c>
-      <c r="C29" s="51" t="n">
+      <c r="C29" s="52" t="n">
         <f aca="false">MIN(A29*Parametres!$B$33,Parametres!$B$34)</f>
         <v>10</v>
       </c>
-      <c r="D29" s="52" t="n">
+      <c r="D29" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B29</f>
         <v>1.22</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="50" t="n">
+      <c r="A30" s="51" t="n">
         <v>7</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">MIN(A30*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0.07</v>
       </c>
-      <c r="C30" s="51" t="n">
+      <c r="C30" s="52" t="n">
         <f aca="false">MIN(A30*Parametres!$B$33,Parametres!$B$34)</f>
         <v>14</v>
       </c>
-      <c r="D30" s="52" t="n">
+      <c r="D30" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B30</f>
         <v>1.24</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="50" t="n">
+      <c r="A31" s="51" t="n">
         <v>10</v>
       </c>
       <c r="B31" s="23" t="n">
         <f aca="false">MIN(A31*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0.1</v>
       </c>
-      <c r="C31" s="51" t="n">
+      <c r="C31" s="52" t="n">
         <f aca="false">MIN(A31*Parametres!$B$33,Parametres!$B$34)</f>
         <v>20</v>
       </c>
-      <c r="D31" s="52" t="n">
+      <c r="D31" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B31</f>
         <v>1.27</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="50" t="n">
+      <c r="A32" s="51" t="n">
         <v>15</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">MIN(A32*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0.15</v>
       </c>
-      <c r="C32" s="51" t="n">
+      <c r="C32" s="52" t="n">
         <f aca="false">MIN(A32*Parametres!$B$33,Parametres!$B$34)</f>
         <v>30</v>
       </c>
-      <c r="D32" s="52" t="n">
+      <c r="D32" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B32</f>
         <v>1.32</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="50" t="n">
+      <c r="A33" s="51" t="n">
         <v>20</v>
       </c>
       <c r="B33" s="23" t="n">
         <f aca="false">MIN(A33*Parametres!$B$31,Parametres!$B$32)</f>
         <v>0.15</v>
       </c>
-      <c r="C33" s="51" t="n">
+      <c r="C33" s="52" t="n">
         <f aca="false">MIN(A33*Parametres!$B$33,Parametres!$B$34)</f>
         <v>30</v>
       </c>
-      <c r="D33" s="52" t="n">
+      <c r="D33" s="53" t="n">
         <f aca="false">1+Parametres!$B$28+Parametres!$B$29+Parametres!$B$30+B33</f>
         <v>1.32</v>
       </c>
@@ -13158,10 +13165,10 @@
       <c r="A39" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="C39" s="53" t="n">
+      <c r="C39" s="54" t="n">
         <f aca="false">IF(B39="Oui",IF(ROW()=39,1,C38+1),0)</f>
         <v>1</v>
       </c>
@@ -13173,7 +13180,7 @@
         <f aca="false">IF(B39="Oui",Parametres!$B$28+Parametres!$B$29+Parametres!$B$30,0)</f>
         <v>0.17</v>
       </c>
-      <c r="F39" s="54" t="n">
+      <c r="F39" s="55" t="n">
         <f aca="false">1+E39+D39</f>
         <v>1.18</v>
       </c>
@@ -13182,10 +13189,10 @@
       <c r="A40" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="B40" s="50" t="s">
+      <c r="B40" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="C40" s="53" t="n">
+      <c r="C40" s="54" t="n">
         <f aca="false">IF(B40="Oui",IF(ROW()=39,1,C39+1),0)</f>
         <v>2</v>
       </c>
@@ -13197,7 +13204,7 @@
         <f aca="false">IF(B40="Oui",Parametres!$B$28+Parametres!$B$29+Parametres!$B$30,0)</f>
         <v>0.17</v>
       </c>
-      <c r="F40" s="54" t="n">
+      <c r="F40" s="55" t="n">
         <f aca="false">1+E40+D40</f>
         <v>1.19</v>
       </c>
@@ -13206,10 +13213,10 @@
       <c r="A41" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="B41" s="50" t="s">
+      <c r="B41" s="51" t="s">
         <v>365</v>
       </c>
-      <c r="C41" s="53" t="n">
+      <c r="C41" s="54" t="n">
         <f aca="false">IF(B41="Oui",IF(ROW()=39,1,C40+1),0)</f>
         <v>0</v>
       </c>
@@ -13221,7 +13228,7 @@
         <f aca="false">IF(B41="Oui",Parametres!$B$28+Parametres!$B$29+Parametres!$B$30,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="54" t="n">
+      <c r="F41" s="55" t="n">
         <f aca="false">1+E41+D41</f>
         <v>1</v>
       </c>
@@ -13230,10 +13237,10 @@
       <c r="A42" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="C42" s="53" t="n">
+      <c r="C42" s="54" t="n">
         <f aca="false">IF(B42="Oui",IF(ROW()=39,1,C41+1),0)</f>
         <v>1</v>
       </c>
@@ -13245,7 +13252,7 @@
         <f aca="false">IF(B42="Oui",Parametres!$B$28+Parametres!$B$29+Parametres!$B$30,0)</f>
         <v>0.17</v>
       </c>
-      <c r="F42" s="54" t="n">
+      <c r="F42" s="55" t="n">
         <f aca="false">1+E42+D42</f>
         <v>1.18</v>
       </c>
@@ -13254,10 +13261,10 @@
       <c r="A43" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="B43" s="50" t="s">
+      <c r="B43" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="C43" s="53" t="n">
+      <c r="C43" s="54" t="n">
         <f aca="false">IF(B43="Oui",IF(ROW()=39,1,C42+1),0)</f>
         <v>2</v>
       </c>
@@ -13269,7 +13276,7 @@
         <f aca="false">IF(B43="Oui",Parametres!$B$28+Parametres!$B$29+Parametres!$B$30,0)</f>
         <v>0.17</v>
       </c>
-      <c r="F43" s="54" t="n">
+      <c r="F43" s="55" t="n">
         <f aca="false">1+E43+D43</f>
         <v>1.19</v>
       </c>
@@ -13278,10 +13285,10 @@
       <c r="A44" s="20" t="s">
         <v>387</v>
       </c>
-      <c r="B44" s="50" t="s">
+      <c r="B44" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="C44" s="53" t="n">
+      <c r="C44" s="54" t="n">
         <f aca="false">IF(B44="Oui",IF(ROW()=39,1,C43+1),0)</f>
         <v>3</v>
       </c>
@@ -13293,7 +13300,7 @@
         <f aca="false">IF(B44="Oui",Parametres!$B$28+Parametres!$B$29+Parametres!$B$30,0)</f>
         <v>0.17</v>
       </c>
-      <c r="F44" s="54" t="n">
+      <c r="F44" s="55" t="n">
         <f aca="false">1+E44+D44</f>
         <v>1.2</v>
       </c>
@@ -13302,10 +13309,10 @@
       <c r="A45" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="B45" s="50" t="s">
+      <c r="B45" s="51" t="s">
         <v>365</v>
       </c>
-      <c r="C45" s="53" t="n">
+      <c r="C45" s="54" t="n">
         <f aca="false">IF(B45="Oui",IF(ROW()=39,1,C44+1),0)</f>
         <v>0</v>
       </c>
@@ -13317,7 +13324,7 @@
         <f aca="false">IF(B45="Oui",Parametres!$B$28+Parametres!$B$29+Parametres!$B$30,0)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="54" t="n">
+      <c r="F45" s="55" t="n">
         <f aca="false">1+E45+D45</f>
         <v>1</v>
       </c>
@@ -13349,7 +13356,7 @@
       <c r="A52" s="20" t="s">
         <v>394</v>
       </c>
-      <c r="B52" s="55" t="n">
+      <c r="B52" s="56" t="n">
         <f aca="false">Parametres!$B$38</f>
         <v>8</v>
       </c>
@@ -13358,7 +13365,7 @@
       <c r="A53" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="B53" s="55" t="n">
+      <c r="B53" s="56" t="n">
         <f aca="false">Parametres!$B$39</f>
         <v>-10</v>
       </c>
@@ -13380,79 +13387,79 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="50" t="n">
+      <c r="A58" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="B58" s="56" t="n">
+      <c r="B58" s="57" t="n">
         <f aca="false">Parametres!$B$40+(1-Parametres!$B$40)*MIN(A58,Parametres!$B$41)/Parametres!$B$41</f>
         <v>0.85</v>
       </c>
-      <c r="C58" s="57" t="str">
+      <c r="C58" s="58" t="str">
         <f aca="false">IF(A58&gt;=Parametres!$B$41,"Plein — aucun malus","Entame")</f>
         <v>Entame</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="50" t="n">
+      <c r="A59" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="B59" s="56" t="n">
+      <c r="B59" s="57" t="n">
         <f aca="false">Parametres!$B$40+(1-Parametres!$B$40)*MIN(A59,Parametres!$B$41)/Parametres!$B$41</f>
         <v>0.8875</v>
       </c>
-      <c r="C59" s="57" t="str">
+      <c r="C59" s="58" t="str">
         <f aca="false">IF(A59&gt;=Parametres!$B$41,"Plein — aucun malus","Entame")</f>
         <v>Entame</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="50" t="n">
+      <c r="A60" s="51" t="n">
         <v>40</v>
       </c>
-      <c r="B60" s="56" t="n">
+      <c r="B60" s="57" t="n">
         <f aca="false">Parametres!$B$40+(1-Parametres!$B$40)*MIN(A60,Parametres!$B$41)/Parametres!$B$41</f>
         <v>0.925</v>
       </c>
-      <c r="C60" s="57" t="str">
+      <c r="C60" s="58" t="str">
         <f aca="false">IF(A60&gt;=Parametres!$B$41,"Plein — aucun malus","Entame")</f>
         <v>Entame</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="50" t="n">
+      <c r="A61" s="51" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="56" t="n">
+      <c r="B61" s="57" t="n">
         <f aca="false">Parametres!$B$40+(1-Parametres!$B$40)*MIN(A61,Parametres!$B$41)/Parametres!$B$41</f>
         <v>0.9625</v>
       </c>
-      <c r="C61" s="57" t="str">
+      <c r="C61" s="58" t="str">
         <f aca="false">IF(A61&gt;=Parametres!$B$41,"Plein — aucun malus","Entame")</f>
         <v>Entame</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="50" t="n">
+      <c r="A62" s="51" t="n">
         <v>80</v>
       </c>
-      <c r="B62" s="56" t="n">
+      <c r="B62" s="57" t="n">
         <f aca="false">Parametres!$B$40+(1-Parametres!$B$40)*MIN(A62,Parametres!$B$41)/Parametres!$B$41</f>
         <v>1</v>
       </c>
-      <c r="C62" s="57" t="str">
+      <c r="C62" s="58" t="str">
         <f aca="false">IF(A62&gt;=Parametres!$B$41,"Plein — aucun malus","Entame")</f>
         <v>Plein — aucun malus</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="50" t="n">
+      <c r="A63" s="51" t="n">
         <v>100</v>
       </c>
-      <c r="B63" s="56" t="n">
+      <c r="B63" s="57" t="n">
         <f aca="false">Parametres!$B$40+(1-Parametres!$B$40)*MIN(A63,Parametres!$B$41)/Parametres!$B$41</f>
         <v>1</v>
       </c>
-      <c r="C63" s="57" t="str">
+      <c r="C63" s="58" t="str">
         <f aca="false">IF(A63&gt;=Parametres!$B$41,"Plein — aucun malus","Entame")</f>
         <v>Plein — aucun malus</v>
       </c>
@@ -13503,7 +13510,7 @@
       <c r="A4" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="B4" s="58" t="n">
+      <c r="B4" s="59" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -13543,7 +13550,7 @@
       <c r="A7" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="57" t="str">
+      <c r="B7" s="58" t="str">
         <f aca="false">IF(A7=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13580,7 +13587,7 @@
       <c r="A8" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="57" t="str">
+      <c r="B8" s="58" t="str">
         <f aca="false">IF(A8=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13617,7 +13624,7 @@
       <c r="A9" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="57" t="str">
+      <c r="B9" s="58" t="str">
         <f aca="false">IF(A9=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13654,7 +13661,7 @@
       <c r="A10" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="57" t="str">
+      <c r="B10" s="58" t="str">
         <f aca="false">IF(A10=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13691,7 +13698,7 @@
       <c r="A11" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="57" t="str">
+      <c r="B11" s="58" t="str">
         <f aca="false">IF(A11=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13728,7 +13735,7 @@
       <c r="A12" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="57" t="str">
+      <c r="B12" s="58" t="str">
         <f aca="false">IF(A12=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13765,7 +13772,7 @@
       <c r="A13" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="57" t="str">
+      <c r="B13" s="58" t="str">
         <f aca="false">IF(A13=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13802,7 +13809,7 @@
       <c r="A14" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="57" t="str">
+      <c r="B14" s="58" t="str">
         <f aca="false">IF(A14=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13839,7 +13846,7 @@
       <c r="A15" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="57" t="str">
+      <c r="B15" s="58" t="str">
         <f aca="false">IF(A15=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>Monstre</v>
       </c>
@@ -13873,38 +13880,38 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="59" t="n">
+      <c r="A16" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="60" t="str">
+      <c r="B16" s="61" t="str">
         <f aca="false">IF(A16=Parametres!$B$51,"BOSS","Monstre")</f>
         <v>BOSS</v>
       </c>
-      <c r="C16" s="61" t="n">
+      <c r="C16" s="62" t="n">
         <f aca="false">ROUND(Parametres!$B$52*A16^Parametres!$B$53*(1+Parametres!$B$58)^($B$4-1)*IF(A16=Parametres!$B$51,Parametres!$B$59,1),0)</f>
         <v>874</v>
       </c>
-      <c r="D16" s="61" t="n">
+      <c r="D16" s="62" t="n">
         <f aca="false">ROUND(Parametres!$B$54*A16^Parametres!$B$55*(1+Parametres!$B$58)^($B$4-1)*IF(A16=Parametres!$B$51,Parametres!$B$60,1),0)</f>
         <v>95</v>
       </c>
-      <c r="E16" s="61" t="n">
+      <c r="E16" s="62" t="n">
         <f aca="false">ROUND(Parametres!$B$56*A16^Parametres!$B$57*(1+Parametres!$B$58)^($B$4-1),0)</f>
         <v>28</v>
       </c>
-      <c r="F16" s="61" t="n">
+      <c r="F16" s="62" t="n">
         <f aca="false">ROUND(Parametres!$B$63*A16*(1+Parametres!$B$64*($B$4-1)),0)</f>
         <v>100</v>
       </c>
-      <c r="G16" s="61" t="n">
+      <c r="G16" s="62" t="n">
         <f aca="false">Parametres!$B$65+IF(A16=Parametres!$B$51,Parametres!$B$66,0)</f>
         <v>6</v>
       </c>
-      <c r="H16" s="62" t="n">
+      <c r="H16" s="63" t="n">
         <f aca="false">H15+F16</f>
         <v>550</v>
       </c>
-      <c r="I16" s="62" t="n">
+      <c r="I16" s="63" t="n">
         <f aca="false">I15+G16</f>
         <v>15</v>
       </c>
@@ -13957,7 +13964,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F21" s="63" t="n">
+      <c r="F21" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A21-1)</f>
         <v>1</v>
       </c>
@@ -13985,7 +13992,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F22" s="64" t="n">
+      <c r="F22" s="65" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A22-1)</f>
         <v>1.2</v>
       </c>
@@ -14011,7 +14018,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F23" s="63" t="n">
+      <c r="F23" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A23-1)</f>
         <v>1.44</v>
       </c>
@@ -14039,7 +14046,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F24" s="64" t="n">
+      <c r="F24" s="65" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A24-1)</f>
         <v>1.728</v>
       </c>
@@ -14065,7 +14072,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F25" s="63" t="n">
+      <c r="F25" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A25-1)</f>
         <v>2.0736</v>
       </c>
@@ -14093,7 +14100,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F26" s="64" t="n">
+      <c r="F26" s="65" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A26-1)</f>
         <v>2.48832</v>
       </c>
@@ -14119,7 +14126,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F27" s="63" t="n">
+      <c r="F27" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A27-1)</f>
         <v>2.985984</v>
       </c>
@@ -14145,7 +14152,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F28" s="64" t="n">
+      <c r="F28" s="65" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A28-1)</f>
         <v>3.5831808</v>
       </c>
@@ -14173,7 +14180,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F29" s="63" t="n">
+      <c r="F29" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A29-1)</f>
         <v>4.29981696</v>
       </c>
@@ -14199,7 +14206,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F30" s="64" t="n">
+      <c r="F30" s="65" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A30-1)</f>
         <v>5.159780352</v>
       </c>
@@ -14225,7 +14232,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F31" s="63" t="n">
+      <c r="F31" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A31-1)</f>
         <v>6.1917364224</v>
       </c>
@@ -14251,7 +14258,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F32" s="64" t="n">
+      <c r="F32" s="65" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A32-1)</f>
         <v>7.43008370688</v>
       </c>
@@ -14279,7 +14286,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F33" s="63" t="n">
+      <c r="F33" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A33-1)</f>
         <v>8.916100448256</v>
       </c>
@@ -14305,7 +14312,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F34" s="64" t="n">
+      <c r="F34" s="65" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A34-1)</f>
         <v>10.6993205379072</v>
       </c>
@@ -14331,7 +14338,7 @@
         <f aca="false">Parametres!$B$65*Parametres!$B$51+Parametres!$B$66</f>
         <v>15</v>
       </c>
-      <c r="F35" s="63" t="n">
+      <c r="F35" s="64" t="n">
         <f aca="false">(1+Parametres!$B$58)^(A35-1)</f>
         <v>12.8391846454886</v>
       </c>
@@ -14375,14 +14382,14 @@
       <c r="A42" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B42" s="65" t="n">
+      <c r="B42" s="66" t="n">
         <v>6</v>
       </c>
       <c r="C42" s="24" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B42)</f>
         <v>1.8</v>
       </c>
-      <c r="D42" s="66" t="n">
+      <c r="D42" s="67" t="n">
         <f aca="false">B42</f>
         <v>6</v>
       </c>
@@ -14394,14 +14401,14 @@
       <c r="A43" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="67" t="n">
+      <c r="B43" s="68" t="n">
         <v>7</v>
       </c>
       <c r="C43" s="31" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B43)</f>
         <v>2.8</v>
       </c>
-      <c r="D43" s="68" t="n">
+      <c r="D43" s="69" t="n">
         <f aca="false">B43-B42</f>
         <v>1</v>
       </c>
@@ -14413,14 +14420,14 @@
       <c r="A44" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="65" t="n">
+      <c r="B44" s="66" t="n">
         <v>8</v>
       </c>
       <c r="C44" s="24" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B44)</f>
         <v>4</v>
       </c>
-      <c r="D44" s="66" t="n">
+      <c r="D44" s="67" t="n">
         <f aca="false">B44-B43</f>
         <v>1</v>
       </c>
@@ -14432,14 +14439,14 @@
       <c r="A45" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B45" s="67" t="n">
+      <c r="B45" s="68" t="n">
         <v>10</v>
       </c>
       <c r="C45" s="31" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B45)</f>
         <v>7.3</v>
       </c>
-      <c r="D45" s="68" t="n">
+      <c r="D45" s="69" t="n">
         <f aca="false">B45-B44</f>
         <v>2</v>
       </c>
@@ -14451,14 +14458,14 @@
       <c r="A46" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B46" s="65" t="n">
+      <c r="B46" s="66" t="n">
         <v>11</v>
       </c>
       <c r="C46" s="24" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B46)</f>
         <v>9.3</v>
       </c>
-      <c r="D46" s="66" t="n">
+      <c r="D46" s="67" t="n">
         <f aca="false">B46-B45</f>
         <v>1</v>
       </c>
@@ -14468,14 +14475,14 @@
       <c r="A47" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B47" s="67" t="n">
+      <c r="B47" s="68" t="n">
         <v>13</v>
       </c>
       <c r="C47" s="31" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B47)</f>
         <v>14.3</v>
       </c>
-      <c r="D47" s="68" t="n">
+      <c r="D47" s="69" t="n">
         <f aca="false">B47-B46</f>
         <v>2</v>
       </c>
@@ -14487,14 +14494,14 @@
       <c r="A48" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B48" s="65" t="n">
+      <c r="B48" s="66" t="n">
         <v>16</v>
       </c>
       <c r="C48" s="24" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B48)</f>
         <v>24.5</v>
       </c>
-      <c r="D48" s="66" t="n">
+      <c r="D48" s="67" t="n">
         <f aca="false">B48-B47</f>
         <v>3</v>
       </c>
@@ -14504,14 +14511,14 @@
       <c r="A49" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B49" s="67" t="n">
+      <c r="B49" s="68" t="n">
         <v>18</v>
       </c>
       <c r="C49" s="31" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B49)</f>
         <v>33.3</v>
       </c>
-      <c r="D49" s="68" t="n">
+      <c r="D49" s="69" t="n">
         <f aca="false">B49-B48</f>
         <v>2</v>
       </c>
@@ -14523,14 +14530,14 @@
       <c r="A50" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B50" s="65" t="n">
+      <c r="B50" s="66" t="n">
         <v>21</v>
       </c>
       <c r="C50" s="24" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B50)</f>
         <v>49.3</v>
       </c>
-      <c r="D50" s="66" t="n">
+      <c r="D50" s="67" t="n">
         <f aca="false">B50-B49</f>
         <v>3</v>
       </c>
@@ -14540,14 +14547,14 @@
       <c r="A51" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B51" s="67" t="n">
+      <c r="B51" s="68" t="n">
         <v>26</v>
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B51)</f>
         <v>85</v>
       </c>
-      <c r="D51" s="68" t="n">
+      <c r="D51" s="69" t="n">
         <f aca="false">B51-B50</f>
         <v>5</v>
       </c>
@@ -14559,14 +14566,14 @@
       <c r="A52" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="65" t="n">
+      <c r="B52" s="66" t="n">
         <v>30</v>
       </c>
       <c r="C52" s="24" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B52)</f>
         <v>120</v>
       </c>
-      <c r="D52" s="66" t="n">
+      <c r="D52" s="67" t="n">
         <f aca="false">B52-B51</f>
         <v>4</v>
       </c>
@@ -14576,14 +14583,14 @@
       <c r="A53" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B53" s="67" t="n">
+      <c r="B53" s="68" t="n">
         <v>35</v>
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">INDEX(Progression!$K$5:$K$54,B53)</f>
         <v>169.5</v>
       </c>
-      <c r="D53" s="68" t="n">
+      <c r="D53" s="69" t="n">
         <f aca="false">B53-B52</f>
         <v>5</v>
       </c>
@@ -14643,13 +14650,13 @@
       <c r="A5" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="59" t="n">
         <v>11</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="44" t="s">
         <v>447</v>
       </c>
-      <c r="E5" s="58" t="n">
+      <c r="E5" s="59" t="n">
         <v>8</v>
       </c>
     </row>
@@ -14657,10 +14664,10 @@
       <c r="A6" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="44" t="s">
         <v>449</v>
       </c>
       <c r="E6" s="9" t="n">
@@ -14671,11 +14678,11 @@
       <c r="A7" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="B7" s="69" t="n">
+      <c r="B7" s="70" t="n">
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$E$5)*$E$6*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>142</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="44" t="s">
         <v>451</v>
       </c>
       <c r="E7" s="9" t="n">
@@ -14686,11 +14693,11 @@
       <c r="A8" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B8" s="69" t="n">
+      <c r="B8" s="70" t="n">
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$E$5)*$E$6*(1+Parametres!$B$58)^($B$6-1)*$E$7,0)</f>
         <v>681</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="44" t="s">
         <v>453</v>
       </c>
       <c r="E8" s="9" t="n">
@@ -14701,7 +14708,7 @@
       <c r="A9" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="B9" s="69" t="n">
+      <c r="B9" s="70" t="n">
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$E$5)*$E$6*(1+Parametres!$B$58)^($B$6-1)*$E$8,0)</f>
         <v>71</v>
       </c>
@@ -14729,7 +14736,7 @@
       <c r="A13" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="B13" s="69" t="n">
+      <c r="B13" s="70" t="n">
         <f aca="false">INDEX(Progression!$D$5:$D$54,MATCH($B$5,Progression!$A$5:$A$54,0))+$B$8</f>
         <v>1131</v>
       </c>
@@ -14738,7 +14745,7 @@
       <c r="A14" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="B14" s="69" t="n">
+      <c r="B14" s="70" t="n">
         <f aca="false">INDEX(Progression!$E$5:$E$54,MATCH($B$5,Progression!$A$5:$A$54,0))+$B$7</f>
         <v>212</v>
       </c>
@@ -14747,7 +14754,7 @@
       <c r="A15" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="B15" s="69" t="n">
+      <c r="B15" s="70" t="n">
         <f aca="false">INDEX(Progression!$F$5:$F$54,MATCH($B$5,Progression!$A$5:$A$54,0))+$B$9</f>
         <v>101</v>
       </c>
@@ -14756,7 +14763,7 @@
       <c r="A16" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="B16" s="70" t="n">
+      <c r="B16" s="71" t="n">
         <f aca="false">INDEX(Progression!$G$5:$G$54,MATCH($B$5,Progression!$A$5:$A$54,0))+$B$10</f>
         <v>0.153225806451613</v>
       </c>
@@ -14765,7 +14772,7 @@
       <c r="A17" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="B17" s="70" t="n">
+      <c r="B17" s="71" t="n">
         <f aca="false">$B$15/($B$15+Parametres!$B$25)</f>
         <v>0.558011049723757</v>
       </c>
@@ -14826,11 +14833,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A21^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>8</v>
       </c>
-      <c r="E21" s="71" t="n">
+      <c r="E21" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D21/(D21+Parametres!$B$25)))</f>
         <v>192.727272727273</v>
       </c>
-      <c r="F21" s="71" t="n">
+      <c r="F21" s="72" t="n">
         <f aca="false">E21*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>214.875366568915</v>
       </c>
@@ -14838,7 +14845,7 @@
         <f aca="false">ROUNDUP(B21/F21,0)</f>
         <v>1</v>
       </c>
-      <c r="H21" s="71" t="n">
+      <c r="H21" s="72" t="n">
         <f aca="false">MAX(1,C21*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>9.2817679558011</v>
       </c>
@@ -14850,7 +14857,7 @@
         <f aca="false">$B$13-I21</f>
         <v>1131</v>
       </c>
-      <c r="K21" s="72" t="str">
+      <c r="K21" s="73" t="str">
         <f aca="false">IF(J21&gt;0,"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -14871,11 +14878,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A22^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>15</v>
       </c>
-      <c r="E22" s="71" t="n">
+      <c r="E22" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D22/(D22+Parametres!$B$25)))</f>
         <v>178.526315789474</v>
       </c>
-      <c r="F22" s="71" t="n">
+      <c r="F22" s="72" t="n">
         <f aca="false">E22*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>199.042444821732</v>
       </c>
@@ -14883,7 +14890,7 @@
         <f aca="false">ROUNDUP(B22/F22,0)</f>
         <v>1</v>
       </c>
-      <c r="H22" s="71" t="n">
+      <c r="H22" s="72" t="n">
         <f aca="false">MAX(1,C22*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>15.9116022099448</v>
       </c>
@@ -14895,7 +14902,7 @@
         <f aca="false">MIN($B$13,J21+ROUND($B$13*Parametres!$B$26,0))-I22</f>
         <v>1131</v>
       </c>
-      <c r="K22" s="72" t="str">
+      <c r="K22" s="73" t="str">
         <f aca="false">IF(AND(K21="OK",J22&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -14916,11 +14923,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A23^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>21</v>
       </c>
-      <c r="E23" s="71" t="n">
+      <c r="E23" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D23/(D23+Parametres!$B$25)))</f>
         <v>167.920792079208</v>
       </c>
-      <c r="F23" s="71" t="n">
+      <c r="F23" s="72" t="n">
         <f aca="false">E23*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>187.218141168956</v>
       </c>
@@ -14928,7 +14935,7 @@
         <f aca="false">ROUNDUP(B23/F23,0)</f>
         <v>2</v>
       </c>
-      <c r="H23" s="71" t="n">
+      <c r="H23" s="72" t="n">
         <f aca="false">MAX(1,C23*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>22.0994475138122</v>
       </c>
@@ -14940,7 +14947,7 @@
         <f aca="false">MIN($B$13,J22+ROUND($B$13*Parametres!$B$26,0))-I23</f>
         <v>1109</v>
       </c>
-      <c r="K23" s="72" t="str">
+      <c r="K23" s="73" t="str">
         <f aca="false">IF(AND(K22="OK",J23&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -14961,11 +14968,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A24^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>27</v>
       </c>
-      <c r="E24" s="71" t="n">
+      <c r="E24" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D24/(D24+Parametres!$B$25)))</f>
         <v>158.504672897196</v>
       </c>
-      <c r="F24" s="71" t="n">
+      <c r="F24" s="72" t="n">
         <f aca="false">E24*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>176.719927645463</v>
       </c>
@@ -14973,7 +14980,7 @@
         <f aca="false">ROUNDUP(B24/F24,0)</f>
         <v>3</v>
       </c>
-      <c r="H24" s="71" t="n">
+      <c r="H24" s="72" t="n">
         <f aca="false">MAX(1,C24*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>27.8453038674033</v>
       </c>
@@ -14985,7 +14992,7 @@
         <f aca="false">MIN($B$13,J23+ROUND($B$13*Parametres!$B$26,0))-I24</f>
         <v>1075</v>
       </c>
-      <c r="K24" s="72" t="str">
+      <c r="K24" s="73" t="str">
         <f aca="false">IF(AND(K23="OK",J24&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -15006,11 +15013,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A25^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>33</v>
       </c>
-      <c r="E25" s="71" t="n">
+      <c r="E25" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D25/(D25+Parametres!$B$25)))</f>
         <v>150.088495575221</v>
       </c>
-      <c r="F25" s="71" t="n">
+      <c r="F25" s="72" t="n">
         <f aca="false">E25*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>167.336568655438</v>
       </c>
@@ -15018,7 +15025,7 @@
         <f aca="false">ROUNDUP(B25/F25,0)</f>
         <v>3</v>
       </c>
-      <c r="H25" s="71" t="n">
+      <c r="H25" s="72" t="n">
         <f aca="false">MAX(1,C25*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>33.1491712707182</v>
       </c>
@@ -15030,7 +15037,7 @@
         <f aca="false">MIN($B$13,J24+ROUND($B$13*Parametres!$B$26,0))-I25</f>
         <v>1065</v>
       </c>
-      <c r="K25" s="72" t="str">
+      <c r="K25" s="73" t="str">
         <f aca="false">IF(AND(K24="OK",J25&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -15051,11 +15058,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A26^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>38</v>
       </c>
-      <c r="E26" s="71" t="n">
+      <c r="E26" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D26/(D26+Parametres!$B$25)))</f>
         <v>143.728813559322</v>
       </c>
-      <c r="F26" s="71" t="n">
+      <c r="F26" s="72" t="n">
         <f aca="false">E26*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>160.246036085293</v>
       </c>
@@ -15063,7 +15070,7 @@
         <f aca="false">ROUNDUP(B26/F26,0)</f>
         <v>4</v>
       </c>
-      <c r="H26" s="71" t="n">
+      <c r="H26" s="72" t="n">
         <f aca="false">MAX(1,C26*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>38.4530386740331</v>
       </c>
@@ -15075,7 +15082,7 @@
         <f aca="false">MIN($B$13,J25+ROUND($B$13*Parametres!$B$26,0))-I26</f>
         <v>1016</v>
       </c>
-      <c r="K26" s="72" t="str">
+      <c r="K26" s="73" t="str">
         <f aca="false">IF(AND(K25="OK",J26&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -15096,11 +15103,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A27^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>43</v>
       </c>
-      <c r="E27" s="71" t="n">
+      <c r="E27" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D27/(D27+Parametres!$B$25)))</f>
         <v>137.886178861789</v>
       </c>
-      <c r="F27" s="71" t="n">
+      <c r="F27" s="72" t="n">
         <f aca="false">E27*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>153.73196957776</v>
       </c>
@@ -15108,7 +15115,7 @@
         <f aca="false">ROUNDUP(B27/F27,0)</f>
         <v>4</v>
       </c>
-      <c r="H27" s="71" t="n">
+      <c r="H27" s="72" t="n">
         <f aca="false">MAX(1,C27*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>43.3149171270718</v>
       </c>
@@ -15120,7 +15127,7 @@
         <f aca="false">MIN($B$13,J26+ROUND($B$13*Parametres!$B$26,0))-I27</f>
         <v>1001</v>
       </c>
-      <c r="K27" s="72" t="str">
+      <c r="K27" s="73" t="str">
         <f aca="false">IF(AND(K26="OK",J27&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -15141,11 +15148,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A28^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>49</v>
       </c>
-      <c r="E28" s="71" t="n">
+      <c r="E28" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D28/(D28+Parametres!$B$25)))</f>
         <v>131.472868217054</v>
       </c>
-      <c r="F28" s="71" t="n">
+      <c r="F28" s="72" t="n">
         <f aca="false">E28*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>146.581645411353</v>
       </c>
@@ -15153,7 +15160,7 @@
         <f aca="false">ROUNDUP(B28/F28,0)</f>
         <v>5</v>
       </c>
-      <c r="H28" s="71" t="n">
+      <c r="H28" s="72" t="n">
         <f aca="false">MAX(1,C28*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>48.1767955801105</v>
       </c>
@@ -15165,7 +15172,7 @@
         <f aca="false">MIN($B$13,J27+ROUND($B$13*Parametres!$B$26,0))-I28</f>
         <v>938</v>
       </c>
-      <c r="K28" s="72" t="str">
+      <c r="K28" s="73" t="str">
         <f aca="false">IF(AND(K27="OK",J28&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -15186,11 +15193,11 @@
         <f aca="false">ROUND(Parametres!$B$56*A29^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>54</v>
       </c>
-      <c r="E29" s="71" t="n">
+      <c r="E29" s="72" t="n">
         <f aca="false">MAX(1,$B$14*(1-D29/(D29+Parametres!$B$25)))</f>
         <v>126.567164179104</v>
       </c>
-      <c r="F29" s="71" t="n">
+      <c r="F29" s="72" t="n">
         <f aca="false">E29*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>141.112181030332</v>
       </c>
@@ -15198,7 +15205,7 @@
         <f aca="false">ROUNDUP(B29/F29,0)</f>
         <v>6</v>
       </c>
-      <c r="H29" s="71" t="n">
+      <c r="H29" s="72" t="n">
         <f aca="false">MAX(1,C29*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>53.0386740331492</v>
       </c>
@@ -15210,52 +15217,52 @@
         <f aca="false">MIN($B$13,J28+ROUND($B$13*Parametres!$B$26,0))-I29</f>
         <v>866</v>
       </c>
-      <c r="K29" s="72" t="str">
+      <c r="K29" s="73" t="str">
         <f aca="false">IF(AND(K28="OK",J29&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="59" t="n">
+      <c r="A30" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="61" t="n">
+      <c r="B30" s="62" t="n">
         <f aca="false">ROUND(Parametres!$B$52*A30^Parametres!$B$53*(1+Parametres!$B$58)^($B$6-1)*IF(A30=Parametres!$B$51,Parametres!$B$59,1),0)</f>
         <v>1812</v>
       </c>
-      <c r="C30" s="61" t="n">
+      <c r="C30" s="62" t="n">
         <f aca="false">ROUND(Parametres!$B$54*A30^Parametres!$B$55*(1+Parametres!$B$58)^($B$6-1)*IF(A30=Parametres!$B$51,Parametres!$B$60,1),0)</f>
         <v>196</v>
       </c>
-      <c r="D30" s="61" t="n">
+      <c r="D30" s="62" t="n">
         <f aca="false">ROUND(Parametres!$B$56*A30^Parametres!$B$57*(1+Parametres!$B$58)^($B$6-1),0)</f>
         <v>59</v>
       </c>
-      <c r="E30" s="73" t="n">
+      <c r="E30" s="74" t="n">
         <f aca="false">MAX(1,$B$14*(1-D30/(D30+Parametres!$B$25)))</f>
         <v>122.014388489209</v>
       </c>
-      <c r="F30" s="73" t="n">
+      <c r="F30" s="74" t="n">
         <f aca="false">E30*(1+$B$16*(Parametres!$B$24-1))</f>
         <v>136.036203295428</v>
       </c>
-      <c r="G30" s="62" t="n">
+      <c r="G30" s="63" t="n">
         <f aca="false">ROUNDUP(B30/F30,0)</f>
         <v>14</v>
       </c>
-      <c r="H30" s="73" t="n">
+      <c r="H30" s="74" t="n">
         <f aca="false">MAX(1,C30*(1-$B$15/($B$15+Parametres!$B$25)))</f>
         <v>86.6298342541437</v>
       </c>
-      <c r="I30" s="62" t="n">
+      <c r="I30" s="63" t="n">
         <f aca="false">ROUND(H30*MAX(0,G30-1),0)</f>
         <v>1126</v>
       </c>
-      <c r="J30" s="74" t="n">
+      <c r="J30" s="75" t="n">
         <f aca="false">MIN($B$13,J29+ROUND($B$13*Parametres!$B$26,0))-I30</f>
         <v>5</v>
       </c>
-      <c r="K30" s="75" t="str">
+      <c r="K30" s="76" t="str">
         <f aca="false">IF(AND(K29="OK",J30&gt;0),"OK","ECHEC")</f>
         <v>OK</v>
       </c>
@@ -15269,7 +15276,7 @@
       <c r="A33" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="B33" s="76" t="n">
+      <c r="B33" s="77" t="n">
         <f aca="false">SUMPRODUCT(MAX((K21:K30="OK")*A21:A30))</f>
         <v>10</v>
       </c>
@@ -15278,7 +15285,7 @@
       <c r="A34" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B34" s="77" t="str">
+      <c r="B34" s="78" t="str">
         <f aca="false">IF(K30="OK","OUI — cycle nettoye","NON — retour au palier 1")</f>
         <v>OUI — cycle nettoye</v>
       </c>
@@ -15287,7 +15294,7 @@
       <c r="A35" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="B35" s="78" t="n">
+      <c r="B35" s="79" t="n">
         <f aca="false">J30</f>
         <v>5</v>
       </c>
@@ -15296,7 +15303,7 @@
       <c r="A36" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="B36" s="77" t="str">
+      <c r="B36" s="78" t="str">
         <f aca="false">IF(J30&gt;$B$13*0.4,"Trop facile — augmente le cycle ou la croissance par cycle",IF(J30&gt;0,"Bien calibre — victoire mais serree","Trop dur — il faut plus de niveau ou d'equipement"))</f>
         <v>Bien calibre — victoire mais serree</v>
       </c>
@@ -15348,7 +15355,7 @@
       <c r="D3" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="E3" s="58" t="n">
+      <c r="E3" s="59" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -15483,7 +15490,7 @@
       <c r="A12" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="D12" s="79" t="n">
+      <c r="D12" s="80" t="n">
         <f aca="false">SUM(D6:D11)</f>
         <v>3.4</v>
       </c>
@@ -15492,7 +15499,7 @@
       <c r="A14" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="I14" s="80" t="s">
+      <c r="I14" s="81" t="s">
         <v>504</v>
       </c>
     </row>
@@ -15558,7 +15565,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A16)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>68</v>
       </c>
-      <c r="G16" s="81" t="n">
+      <c r="G16" s="82" t="n">
         <f aca="false">F16/B16</f>
         <v>6.8</v>
       </c>
@@ -15607,7 +15614,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A17)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>95</v>
       </c>
-      <c r="G17" s="82" t="n">
+      <c r="G17" s="83" t="n">
         <f aca="false">F17/B17</f>
         <v>6.78571428571429</v>
       </c>
@@ -15656,7 +15663,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A18)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>122</v>
       </c>
-      <c r="G18" s="81" t="n">
+      <c r="G18" s="82" t="n">
         <f aca="false">F18/B18</f>
         <v>6.77777777777778</v>
       </c>
@@ -15705,7 +15712,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A19)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>150</v>
       </c>
-      <c r="G19" s="82" t="n">
+      <c r="G19" s="83" t="n">
         <f aca="false">F19/B19</f>
         <v>6.81818181818182</v>
       </c>
@@ -15754,7 +15761,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A20)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>177</v>
       </c>
-      <c r="G20" s="81" t="n">
+      <c r="G20" s="82" t="n">
         <f aca="false">F20/B20</f>
         <v>6.80769230769231</v>
       </c>
@@ -15803,7 +15810,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A21)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>204</v>
       </c>
-      <c r="G21" s="82" t="n">
+      <c r="G21" s="83" t="n">
         <f aca="false">F21/B21</f>
         <v>6.8</v>
       </c>
@@ -15852,7 +15859,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A22)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>231</v>
       </c>
-      <c r="G22" s="81" t="n">
+      <c r="G22" s="82" t="n">
         <f aca="false">F22/B22</f>
         <v>6.79411764705882</v>
       </c>
@@ -15901,7 +15908,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A23)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>258</v>
       </c>
-      <c r="G23" s="82" t="n">
+      <c r="G23" s="83" t="n">
         <f aca="false">F23/B23</f>
         <v>6.78947368421053</v>
       </c>
@@ -15950,7 +15957,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A24)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>286</v>
       </c>
-      <c r="G24" s="81" t="n">
+      <c r="G24" s="82" t="n">
         <f aca="false">F24/B24</f>
         <v>6.80952380952381</v>
       </c>
@@ -15999,7 +16006,7 @@
         <f aca="false">ROUND((Parametres!$B$86+Parametres!$B$87*$A25)*Parametres!$B$92*(1+Parametres!$B$58)^($E$3-1),0)</f>
         <v>313</v>
       </c>
-      <c r="G25" s="82" t="n">
+      <c r="G25" s="83" t="n">
         <f aca="false">F25/B25</f>
         <v>6.80434782608696</v>
       </c>
@@ -16068,11 +16075,11 @@
       <c r="A32" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="B32" s="83" t="n">
+      <c r="B32" s="84" t="n">
         <f aca="false">A32*Parametres!$B$93</f>
         <v>0</v>
       </c>
-      <c r="C32" s="84" t="n">
+      <c r="C32" s="85" t="n">
         <f aca="false">1+B32</f>
         <v>1</v>
       </c>
@@ -16093,11 +16100,11 @@
       <c r="A33" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="85" t="n">
+      <c r="B33" s="86" t="n">
         <f aca="false">A33*Parametres!$B$93</f>
         <v>0.08</v>
       </c>
-      <c r="C33" s="86" t="n">
+      <c r="C33" s="87" t="n">
         <f aca="false">1+B33</f>
         <v>1.08</v>
       </c>
@@ -16118,11 +16125,11 @@
       <c r="A34" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="83" t="n">
+      <c r="B34" s="84" t="n">
         <f aca="false">A34*Parametres!$B$93</f>
         <v>0.16</v>
       </c>
-      <c r="C34" s="84" t="n">
+      <c r="C34" s="85" t="n">
         <f aca="false">1+B34</f>
         <v>1.16</v>
       </c>
@@ -16143,11 +16150,11 @@
       <c r="A35" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="85" t="n">
+      <c r="B35" s="86" t="n">
         <f aca="false">A35*Parametres!$B$93</f>
         <v>0.24</v>
       </c>
-      <c r="C35" s="86" t="n">
+      <c r="C35" s="87" t="n">
         <f aca="false">1+B35</f>
         <v>1.24</v>
       </c>
@@ -16168,11 +16175,11 @@
       <c r="A36" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="83" t="n">
+      <c r="B36" s="84" t="n">
         <f aca="false">A36*Parametres!$B$93</f>
         <v>0.32</v>
       </c>
-      <c r="C36" s="84" t="n">
+      <c r="C36" s="85" t="n">
         <f aca="false">1+B36</f>
         <v>1.32</v>
       </c>
@@ -16193,11 +16200,11 @@
       <c r="A37" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="85" t="n">
+      <c r="B37" s="86" t="n">
         <f aca="false">A37*Parametres!$B$93</f>
         <v>0.4</v>
       </c>
-      <c r="C37" s="86" t="n">
+      <c r="C37" s="87" t="n">
         <f aca="false">1+B37</f>
         <v>1.4</v>
       </c>
@@ -16218,11 +16225,11 @@
       <c r="A38" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="83" t="n">
+      <c r="B38" s="84" t="n">
         <f aca="false">A38*Parametres!$B$93</f>
         <v>0.48</v>
       </c>
-      <c r="C38" s="84" t="n">
+      <c r="C38" s="85" t="n">
         <f aca="false">1+B38</f>
         <v>1.48</v>
       </c>
@@ -16243,11 +16250,11 @@
       <c r="A39" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="85" t="n">
+      <c r="B39" s="86" t="n">
         <f aca="false">A39*Parametres!$B$93</f>
         <v>0.56</v>
       </c>
-      <c r="C39" s="86" t="n">
+      <c r="C39" s="87" t="n">
         <f aca="false">1+B39</f>
         <v>1.56</v>
       </c>
@@ -16268,11 +16275,11 @@
       <c r="A40" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="83" t="n">
+      <c r="B40" s="84" t="n">
         <f aca="false">A40*Parametres!$B$93</f>
         <v>0.64</v>
       </c>
-      <c r="C40" s="84" t="n">
+      <c r="C40" s="85" t="n">
         <f aca="false">1+B40</f>
         <v>1.64</v>
       </c>
@@ -16293,11 +16300,11 @@
       <c r="A41" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B41" s="85" t="n">
+      <c r="B41" s="86" t="n">
         <f aca="false">A41*Parametres!$B$93</f>
         <v>0.72</v>
       </c>
-      <c r="C41" s="86" t="n">
+      <c r="C41" s="87" t="n">
         <f aca="false">1+B41</f>
         <v>1.72</v>
       </c>
@@ -16318,11 +16325,11 @@
       <c r="A42" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B42" s="83" t="n">
+      <c r="B42" s="84" t="n">
         <f aca="false">A42*Parametres!$B$93</f>
         <v>0.8</v>
       </c>
-      <c r="C42" s="84" t="n">
+      <c r="C42" s="85" t="n">
         <f aca="false">1+B42</f>
         <v>1.8</v>
       </c>
@@ -16414,14 +16421,14 @@
       <c r="A6" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="B6" s="63" t="n">
+      <c r="B6" s="64" t="n">
         <f aca="false">Parametres!$B$88</f>
         <v>1</v>
       </c>
       <c r="C6" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="87" t="n">
+      <c r="D6" s="88" t="n">
         <f aca="false">Parametres!$B$107^C6</f>
         <v>1</v>
       </c>
@@ -16429,7 +16436,7 @@
         <f aca="false">Parametres!$B$75</f>
         <v>70</v>
       </c>
-      <c r="F6" s="88" t="n">
+      <c r="F6" s="89" t="n">
         <f aca="false">E6/SUM($E$6:$E$10)</f>
         <v>0.7</v>
       </c>
@@ -16441,14 +16448,14 @@
       <c r="A7" s="27" t="s">
         <v>507</v>
       </c>
-      <c r="B7" s="64" t="n">
+      <c r="B7" s="65" t="n">
         <f aca="false">Parametres!$B$89</f>
         <v>1.6</v>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="89" t="n">
+      <c r="D7" s="90" t="n">
         <f aca="false">Parametres!$B$107^C7</f>
         <v>3</v>
       </c>
@@ -16456,7 +16463,7 @@
         <f aca="false">Parametres!$B$76</f>
         <v>22</v>
       </c>
-      <c r="F7" s="90" t="n">
+      <c r="F7" s="91" t="n">
         <f aca="false">E7/SUM($E$6:$E$10)</f>
         <v>0.22</v>
       </c>
@@ -16468,14 +16475,14 @@
       <c r="A8" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="B8" s="63" t="n">
+      <c r="B8" s="64" t="n">
         <f aca="false">Parametres!$B$90</f>
         <v>2.6</v>
       </c>
       <c r="C8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="87" t="n">
+      <c r="D8" s="88" t="n">
         <f aca="false">Parametres!$B$107^C8</f>
         <v>9</v>
       </c>
@@ -16483,7 +16490,7 @@
         <f aca="false">Parametres!$B$77</f>
         <v>6.5</v>
       </c>
-      <c r="F8" s="88" t="n">
+      <c r="F8" s="89" t="n">
         <f aca="false">E8/SUM($E$6:$E$10)</f>
         <v>0.065</v>
       </c>
@@ -16495,14 +16502,14 @@
       <c r="A9" s="27" t="s">
         <v>509</v>
       </c>
-      <c r="B9" s="64" t="n">
+      <c r="B9" s="65" t="n">
         <f aca="false">Parametres!$B$91</f>
         <v>4.2</v>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="89" t="n">
+      <c r="D9" s="90" t="n">
         <f aca="false">Parametres!$B$107^C9</f>
         <v>27</v>
       </c>
@@ -16510,7 +16517,7 @@
         <f aca="false">Parametres!$B$78</f>
         <v>1.4</v>
       </c>
-      <c r="F9" s="90" t="n">
+      <c r="F9" s="91" t="n">
         <f aca="false">E9/SUM($E$6:$E$10)</f>
         <v>0.014</v>
       </c>
@@ -16522,14 +16529,14 @@
       <c r="A10" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="B10" s="63" t="n">
+      <c r="B10" s="64" t="n">
         <f aca="false">Parametres!$B$92</f>
         <v>6.8</v>
       </c>
       <c r="C10" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="87" t="n">
+      <c r="D10" s="88" t="n">
         <f aca="false">Parametres!$B$107^C10</f>
         <v>81</v>
       </c>
@@ -16537,7 +16544,7 @@
         <f aca="false">Parametres!$B$79</f>
         <v>0.1</v>
       </c>
-      <c r="F10" s="88" t="n">
+      <c r="F10" s="89" t="n">
         <f aca="false">E10/SUM($E$6:$E$10)</f>
         <v>0.001</v>
       </c>
@@ -16559,7 +16566,7 @@
       <c r="A15" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="B15" s="91" t="n">
+      <c r="B15" s="92" t="n">
         <f aca="false">ROUND(Parametres!$B$111*Parametres!$B$74,1)</f>
         <v>5.6</v>
       </c>
@@ -16568,7 +16575,7 @@
       <c r="A16" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="B16" s="92" t="n">
+      <c r="B16" s="93" t="n">
         <f aca="false">ROUND(B15/Parametres!$B$108,2)</f>
         <v>0.93</v>
       </c>
@@ -16577,7 +16584,7 @@
       <c r="A17" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="B17" s="92" t="n">
+      <c r="B17" s="93" t="n">
         <f aca="false">SUMPRODUCT($F$6:$F$10,$D$6:$D$10)</f>
         <v>2.404</v>
       </c>
@@ -16586,7 +16593,7 @@
       <c r="A18" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="B18" s="92" t="n">
+      <c r="B18" s="93" t="n">
         <f aca="false">B16*B17</f>
         <v>2.23572</v>
       </c>
@@ -16738,14 +16745,14 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="50" t="n">
+      <c r="A31" s="51" t="n">
         <v>0</v>
       </c>
       <c r="B31" s="23" t="n">
         <f aca="false">A31*Parametres!$B$109</f>
         <v>0</v>
       </c>
-      <c r="C31" s="93" t="n">
+      <c r="C31" s="94" t="n">
         <f aca="false">ROUND($D$10*B31,1)</f>
         <v>0</v>
       </c>
@@ -16755,14 +16762,14 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="50" t="n">
+      <c r="A32" s="51" t="n">
         <v>10</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">A32*Parametres!$B$109</f>
         <v>0.05</v>
       </c>
-      <c r="C32" s="93" t="n">
+      <c r="C32" s="94" t="n">
         <f aca="false">ROUND($D$10*B32,1)</f>
         <v>4.1</v>
       </c>
@@ -16772,14 +16779,14 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="50" t="n">
+      <c r="A33" s="51" t="n">
         <v>20</v>
       </c>
       <c r="B33" s="23" t="n">
         <f aca="false">A33*Parametres!$B$109</f>
         <v>0.1</v>
       </c>
-      <c r="C33" s="93" t="n">
+      <c r="C33" s="94" t="n">
         <f aca="false">ROUND($D$10*B33,1)</f>
         <v>8.1</v>
       </c>
@@ -16789,14 +16796,14 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="50" t="n">
+      <c r="A34" s="51" t="n">
         <v>30</v>
       </c>
       <c r="B34" s="23" t="n">
         <f aca="false">A34*Parametres!$B$109</f>
         <v>0.15</v>
       </c>
-      <c r="C34" s="93" t="n">
+      <c r="C34" s="94" t="n">
         <f aca="false">ROUND($D$10*B34,1)</f>
         <v>12.2</v>
       </c>
@@ -16806,14 +16813,14 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="50" t="n">
+      <c r="A35" s="51" t="n">
         <v>45</v>
       </c>
       <c r="B35" s="23" t="n">
         <f aca="false">A35*Parametres!$B$109</f>
         <v>0.225</v>
       </c>
-      <c r="C35" s="93" t="n">
+      <c r="C35" s="94" t="n">
         <f aca="false">ROUND($D$10*B35,1)</f>
         <v>18.2</v>
       </c>
@@ -16839,45 +16846,45 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="44" t="s">
         <v>563</v>
       </c>
-      <c r="B39" s="69" t="n">
+      <c r="B39" s="70" t="n">
         <f aca="false">Equipement!$I$23</f>
         <v>57</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="44" t="s">
         <v>564</v>
       </c>
-      <c r="B40" s="69" t="n">
+      <c r="B40" s="70" t="n">
         <f aca="false">Parametres!$B$67</f>
         <v>3000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="44" t="s">
         <v>565</v>
       </c>
-      <c r="B41" s="94" t="n">
+      <c r="B41" s="95" t="n">
         <f aca="false">ROUND(B40/B39,0)</f>
         <v>53</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="44" t="s">
         <v>566</v>
       </c>
-      <c r="B42" s="95" t="n">
+      <c r="B42" s="96" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="44" t="s">
         <v>567</v>
       </c>
-      <c r="B43" s="94" t="n">
+      <c r="B43" s="95" t="n">
         <f aca="false">B41</f>
         <v>53</v>
       </c>
@@ -16891,42 +16898,42 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="44" t="s">
         <v>570</v>
       </c>
-      <c r="B46" s="96" t="s">
+      <c r="B46" s="97" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="44" t="s">
         <v>572</v>
       </c>
-      <c r="B47" s="96" t="s">
+      <c r="B47" s="97" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="43" t="s">
+      <c r="A48" s="44" t="s">
         <v>574</v>
       </c>
-      <c r="B48" s="96" t="s">
+      <c r="B48" s="97" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="43" t="s">
+      <c r="A49" s="44" t="s">
         <v>576</v>
       </c>
-      <c r="B49" s="96" t="s">
+      <c r="B49" s="97" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="43" t="s">
+      <c r="A50" s="44" t="s">
         <v>578</v>
       </c>
-      <c r="B50" s="96" t="s">
+      <c r="B50" s="97" t="s">
         <v>579</v>
       </c>
     </row>
@@ -16968,7 +16975,7 @@
       <c r="C56" s="37" t="n">
         <v>27</v>
       </c>
-      <c r="D56" s="97" t="n">
+      <c r="D56" s="98" t="n">
         <f aca="false">B56*C56</f>
         <v>5400</v>
       </c>
@@ -16988,7 +16995,7 @@
       <c r="C57" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="D57" s="97" t="n">
+      <c r="D57" s="98" t="n">
         <f aca="false">B57*C57</f>
         <v>5400</v>
       </c>
@@ -17008,7 +17015,7 @@
       <c r="C58" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="D58" s="97" t="n">
+      <c r="D58" s="98" t="n">
         <f aca="false">B58*C58</f>
         <v>5400</v>
       </c>
@@ -17028,7 +17035,7 @@
       <c r="C59" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="97" t="n">
+      <c r="D59" s="98" t="n">
         <f aca="false">B59*C59</f>
         <v>5400</v>
       </c>
@@ -17041,15 +17048,15 @@
       <c r="A60" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="C60" s="98" t="n">
+      <c r="C60" s="99" t="n">
         <f aca="false">SUM(C56:C59)</f>
         <v>40</v>
       </c>
-      <c r="D60" s="99" t="n">
+      <c r="D60" s="100" t="n">
         <f aca="false">SUM(D56:D59)</f>
         <v>21600</v>
       </c>
-      <c r="E60" s="100" t="n">
+      <c r="E60" s="101" t="n">
         <f aca="false">SUM(E56:E59)</f>
         <v>6.4</v>
       </c>
